--- a/Deliverables/BOM/PCBWay-BOM_20.pcs.xlsx
+++ b/Deliverables/BOM/PCBWay-BOM_20.pcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12AF564-8070-4E95-AA91-2188E6602CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E114134-175D-4FE0-AF94-AAFB86D1296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="255">
   <si>
     <t>Component list</t>
   </si>
@@ -615,9 +615,6 @@
     <t>11.3K</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>LCSC Part Number</t>
   </si>
   <si>
@@ -784,6 +781,12 @@
   </si>
   <si>
     <t>Quantity (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity Per Board</t>
+  </si>
+  <si>
+    <t>Quantity (20 Boards)</t>
   </si>
 </sst>
 </file>
@@ -1317,15 +1320,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1371,24 +1365,24 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1396,6 +1390,15 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1424,13 +1427,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>1952625</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1478,13 +1481,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>1876425</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1532,13 +1535,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1846,7 +1849,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="21" customWidth="1"/>
@@ -1858,12 +1861,13 @@
     <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1873,12 +1877,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-    </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="16"/>
       <c r="C2" s="37"/>
@@ -1895,35 +1900,37 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="3"/>
+      <c r="N2" s="34"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="65" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="46"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G3" s="61"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="73"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="17"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="64" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="43" t="s">
         <v>6</v>
       </c>
@@ -1932,17 +1939,18 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="47"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="74"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="44" t="s">
         <v>7</v>
       </c>
@@ -1952,9 +1960,10 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="47"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="4"/>
+      <c r="N5" s="74"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="18"/>
       <c r="C6" s="38"/>
@@ -1967,39 +1976,42 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="47"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="4"/>
+      <c r="N6" s="74"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="47"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="74"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="47"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="74"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
@@ -2023,28 +2035,31 @@
         <v>160</v>
       </c>
       <c r="I9" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="K9" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="M9" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="K9" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
+      <c r="N9" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="45"/>
       <c r="B10" s="41">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="30" t="s">
@@ -2053,36 +2068,40 @@
       <c r="E10" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="70" t="s">
         <v>131</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="J10" s="53" t="s">
+      <c r="I10" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="J10" s="50" t="s">
         <v>178</v>
       </c>
       <c r="K10" s="30">
         <v>20</v>
       </c>
-      <c r="L10" s="53">
+      <c r="L10" s="47">
+        <f>K10*20</f>
+        <v>400</v>
+      </c>
+      <c r="M10" s="50">
         <v>450</v>
       </c>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
+      <c r="N10" s="30"/>
+    </row>
+    <row r="11" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B51" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="32" t="s">
@@ -2101,26 +2120,30 @@
         <v>162</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="J11" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="J11" s="51" t="s">
         <v>179</v>
       </c>
       <c r="K11" s="32">
         <v>1</v>
       </c>
-      <c r="L11" s="54">
+      <c r="L11" s="32">
+        <f t="shared" ref="L11:L51" si="1">K11*20</f>
+        <v>20</v>
+      </c>
+      <c r="M11" s="51">
         <v>40</v>
       </c>
-      <c r="M11" s="32"/>
-    </row>
-    <row r="12" spans="1:13" s="49" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" spans="1:14" s="46" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="45"/>
       <c r="B12" s="41">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -2129,36 +2152,40 @@
       <c r="E12" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="70" t="s">
         <v>133</v>
       </c>
       <c r="H12" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I12" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="J12" s="53" t="s">
+      <c r="I12" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="J12" s="50" t="s">
         <v>180</v>
       </c>
       <c r="K12" s="30">
         <v>43</v>
       </c>
-      <c r="L12" s="53">
+      <c r="L12" s="47">
+        <f>K12*20</f>
+        <v>860</v>
+      </c>
+      <c r="M12" s="50">
         <v>900</v>
       </c>
-      <c r="M12" s="30"/>
-    </row>
-    <row r="13" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
+      <c r="N12" s="30"/>
+    </row>
+    <row r="13" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="45"/>
       <c r="B13" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -2177,26 +2204,30 @@
         <v>161</v>
       </c>
       <c r="I13" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>181</v>
       </c>
       <c r="K13" s="32">
         <v>12</v>
       </c>
-      <c r="L13" s="54">
+      <c r="L13" s="32">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+      <c r="M13" s="51">
         <v>300</v>
       </c>
-      <c r="M13" s="32"/>
-    </row>
-    <row r="14" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="45"/>
       <c r="B14" s="41">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -2205,36 +2236,40 @@
       <c r="E14" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="70" t="s">
         <v>135</v>
       </c>
       <c r="H14" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="I14" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" s="53" t="s">
+      <c r="I14" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="50" t="s">
         <v>182</v>
       </c>
       <c r="K14" s="30">
         <v>2</v>
       </c>
-      <c r="L14" s="53">
+      <c r="L14" s="47">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="M14" s="50">
         <v>45</v>
       </c>
-      <c r="M14" s="30"/>
-    </row>
-    <row r="15" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
+      <c r="N14" s="30"/>
+    </row>
+    <row r="15" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="45"/>
       <c r="B15" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -2246,33 +2281,37 @@
       <c r="F15" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="71" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>161</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="J15" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J15" s="51" t="s">
         <v>183</v>
       </c>
       <c r="K15" s="32">
         <v>16</v>
       </c>
-      <c r="L15" s="54">
+      <c r="L15" s="32">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="M15" s="51">
         <v>400</v>
       </c>
-      <c r="M15" s="32"/>
-    </row>
-    <row r="16" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="45"/>
       <c r="B16" s="41">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -2281,36 +2320,40 @@
       <c r="E16" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="70" t="s">
         <v>137</v>
       </c>
       <c r="H16" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="J16" s="53" t="s">
+      <c r="I16" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="50" t="s">
         <v>184</v>
       </c>
       <c r="K16" s="30">
         <v>1</v>
       </c>
-      <c r="L16" s="53">
+      <c r="L16" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M16" s="50">
         <v>30</v>
       </c>
-      <c r="M16" s="30"/>
-    </row>
-    <row r="17" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
+      <c r="N16" s="30"/>
+    </row>
+    <row r="17" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="45"/>
       <c r="B17" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="32" t="s">
@@ -2329,26 +2372,30 @@
         <v>161</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="J17" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" s="51" t="s">
         <v>185</v>
       </c>
       <c r="K17" s="32">
         <v>6</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="32">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="M17" s="51">
         <v>200</v>
       </c>
-      <c r="M17" s="32"/>
-    </row>
-    <row r="18" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+      <c r="N17" s="32"/>
+    </row>
+    <row r="18" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
       <c r="B18" s="41">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="30" t="s">
@@ -2357,36 +2404,40 @@
       <c r="E18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="56" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="I18" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="J18" s="53" t="s">
+      <c r="I18" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K18" s="30">
         <v>7</v>
       </c>
-      <c r="L18" s="53">
+      <c r="L18" s="47">
+        <f>K18*20</f>
+        <v>140</v>
+      </c>
+      <c r="M18" s="50">
         <v>160</v>
       </c>
-      <c r="M18" s="30"/>
-    </row>
-    <row r="19" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
+      <c r="N18" s="30"/>
+    </row>
+    <row r="19" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="45"/>
       <c r="B19" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="32" t="s">
@@ -2405,26 +2456,30 @@
         <v>161</v>
       </c>
       <c r="I19" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="J19" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="J19" s="51" t="s">
         <v>187</v>
       </c>
       <c r="K19" s="32">
         <v>4</v>
       </c>
-      <c r="L19" s="54">
+      <c r="L19" s="32">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="M19" s="51">
         <v>100</v>
       </c>
-      <c r="M19" s="32"/>
-    </row>
-    <row r="20" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
+      <c r="N19" s="32"/>
+    </row>
+    <row r="20" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="45"/>
       <c r="B20" s="41">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="30" t="s">
@@ -2433,36 +2488,40 @@
       <c r="E20" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="70" t="s">
         <v>141</v>
       </c>
       <c r="H20" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" s="53" t="s">
+      <c r="I20" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="50" t="s">
         <v>188</v>
       </c>
       <c r="K20" s="30">
         <v>1</v>
       </c>
-      <c r="L20" s="53">
+      <c r="L20" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M20" s="50">
         <v>100</v>
       </c>
-      <c r="M20" s="30"/>
-    </row>
-    <row r="21" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48"/>
+      <c r="N20" s="30"/>
+    </row>
+    <row r="21" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="45"/>
       <c r="B21" s="41">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="32" t="s">
@@ -2481,26 +2540,30 @@
         <v>161</v>
       </c>
       <c r="I21" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="J21" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="51" t="s">
         <v>189</v>
       </c>
       <c r="K21" s="32">
         <v>8</v>
       </c>
-      <c r="L21" s="54">
+      <c r="L21" s="32">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M21" s="51">
         <v>200</v>
       </c>
-      <c r="M21" s="32"/>
-    </row>
-    <row r="22" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="45"/>
       <c r="B22" s="41">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="30" t="s">
@@ -2509,36 +2572,40 @@
       <c r="E22" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="73" t="s">
+      <c r="G22" s="70" t="s">
         <v>143</v>
       </c>
       <c r="H22" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="J22" s="53" t="s">
+      <c r="I22" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="J22" s="50" t="s">
         <v>183</v>
       </c>
       <c r="K22" s="30">
         <v>8</v>
       </c>
-      <c r="L22" s="53">
+      <c r="L22" s="47">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M22" s="50">
         <v>200</v>
       </c>
-      <c r="M22" s="30"/>
-    </row>
-    <row r="23" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+      <c r="N22" s="30"/>
+    </row>
+    <row r="23" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="45"/>
       <c r="B23" s="41">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="32" t="s">
@@ -2557,26 +2624,30 @@
         <v>164</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="J23" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>186</v>
       </c>
       <c r="K23" s="32">
         <v>8</v>
       </c>
-      <c r="L23" s="54">
+      <c r="L23" s="32">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M23" s="51">
         <v>170</v>
       </c>
-      <c r="M23" s="32"/>
-    </row>
-    <row r="24" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
+      <c r="N23" s="32"/>
+    </row>
+    <row r="24" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="45"/>
       <c r="B24" s="41">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="30" t="s">
@@ -2585,37 +2656,41 @@
       <c r="E24" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="70" t="s">
         <v>145</v>
       </c>
       <c r="H24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I24" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="J24" s="53" t="s">
+      <c r="I24" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="J24" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K24" s="30">
         <v>4</v>
       </c>
-      <c r="L24" s="53">
+      <c r="L24" s="47">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="M24" s="50">
         <v>100</v>
       </c>
-      <c r="M24" s="30"/>
-    </row>
-    <row r="25" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
+      <c r="N24" s="30"/>
+    </row>
+    <row r="25" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="45"/>
       <c r="B25" s="41">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
-        <v>237</v>
+      <c r="C25" s="58" t="s">
+        <v>236</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>30</v>
@@ -2624,7 +2699,7 @@
         <v>73</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>107</v>
@@ -2633,27 +2708,31 @@
         <v>166</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="J25" s="54" t="s">
-        <v>201</v>
+        <v>217</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K25" s="32">
         <v>1</v>
       </c>
-      <c r="L25" s="54">
+      <c r="L25" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M25" s="51">
         <v>30</v>
       </c>
-      <c r="M25" s="32"/>
-    </row>
-    <row r="26" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="45"/>
       <c r="B26" s="41">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>237</v>
+      <c r="C26" s="57" t="s">
+        <v>236</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>31</v>
@@ -2661,37 +2740,41 @@
       <c r="E26" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="73" t="s">
+      <c r="G26" s="70" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I26" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>201</v>
+      <c r="I26" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="J26" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K26" s="30">
         <v>1</v>
       </c>
-      <c r="L26" s="53">
+      <c r="L26" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M26" s="50">
         <v>30</v>
       </c>
-      <c r="M26" s="30"/>
-    </row>
-    <row r="27" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
+      <c r="N26" s="30"/>
+    </row>
+    <row r="27" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
       <c r="B27" s="41">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>238</v>
+      <c r="C27" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D27" s="32" t="s">
         <v>32</v>
@@ -2702,33 +2785,37 @@
       <c r="F27" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="74" t="s">
+      <c r="G27" s="71" t="s">
         <v>147</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>168</v>
       </c>
       <c r="I27" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="J27" s="54" t="s">
-        <v>201</v>
+        <v>219</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K27" s="32">
         <v>1</v>
       </c>
-      <c r="L27" s="54">
+      <c r="L27" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M27" s="51">
         <v>40</v>
       </c>
-      <c r="M27" s="32"/>
-    </row>
-    <row r="28" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
+      <c r="N27" s="32"/>
+    </row>
+    <row r="28" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
       <c r="B28" s="41">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="57" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="30" t="s">
@@ -2737,36 +2824,40 @@
       <c r="E28" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G28" s="73" t="s">
+      <c r="F28" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="70" t="s">
         <v>110</v>
       </c>
       <c r="H28" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="I28" s="50" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>201</v>
+      <c r="I28" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="J28" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K28" s="30">
         <v>1</v>
       </c>
-      <c r="L28" s="53">
+      <c r="L28" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M28" s="50">
         <v>30</v>
       </c>
-      <c r="M28" s="30"/>
-    </row>
-    <row r="29" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
+      <c r="N28" s="30"/>
+    </row>
+    <row r="29" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
       <c r="B29" s="41">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="32" t="s">
@@ -2776,7 +2867,7 @@
         <v>77</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>111</v>
@@ -2785,26 +2876,30 @@
         <v>170</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J29" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K29" s="32">
         <v>8</v>
       </c>
-      <c r="L29" s="54">
+      <c r="L29" s="32">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M29" s="51">
         <v>180</v>
       </c>
-      <c r="M29" s="32"/>
-    </row>
-    <row r="30" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
+      <c r="N29" s="32"/>
+    </row>
+    <row r="30" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="45"/>
       <c r="B30" s="41">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="57" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="30" t="s">
@@ -2813,33 +2908,37 @@
       <c r="E30" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" s="73" t="s">
+      <c r="F30" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G30" s="70" t="s">
         <v>112</v>
       </c>
       <c r="H30" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="50"/>
-      <c r="J30" s="53" t="s">
-        <v>201</v>
+      <c r="I30" s="47"/>
+      <c r="J30" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K30" s="30">
         <v>4</v>
       </c>
-      <c r="L30" s="53"/>
-      <c r="M30" s="30"/>
-    </row>
-    <row r="31" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
+      <c r="L30" s="47">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="M30" s="50"/>
+      <c r="N30" s="30"/>
+    </row>
+    <row r="31" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="45"/>
       <c r="B31" s="41">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
-        <v>238</v>
+      <c r="C31" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>36</v>
@@ -2850,72 +2949,80 @@
       <c r="F31" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="74">
+      <c r="G31" s="71">
         <v>61300611121</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>171</v>
       </c>
       <c r="I31" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="J31" s="54" t="s">
-        <v>201</v>
+        <v>221</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K31" s="32">
         <v>1</v>
       </c>
-      <c r="L31" s="54">
+      <c r="L31" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M31" s="51">
         <v>40</v>
       </c>
-      <c r="M31" s="32"/>
-    </row>
-    <row r="32" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="48"/>
+      <c r="N31" s="32"/>
+    </row>
+    <row r="32" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
       <c r="B32" s="41">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="C32" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G32" s="59" t="s">
+      <c r="F32" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="I32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J32" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K32" s="56">
+      <c r="H32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="53">
         <v>5</v>
       </c>
-      <c r="L32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="M32" s="52"/>
-    </row>
-    <row r="33" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
+      <c r="L32" s="49">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="M32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="N32" s="49"/>
+    </row>
+    <row r="33" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="45"/>
       <c r="B33" s="41">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="62" t="s">
-        <v>240</v>
+      <c r="C33" s="59" t="s">
+        <v>239</v>
       </c>
       <c r="D33" s="32" t="s">
         <v>38</v>
@@ -2923,37 +3030,41 @@
       <c r="E33" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="74" t="s">
+      <c r="G33" s="71" t="s">
         <v>148</v>
       </c>
       <c r="H33" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="I33" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="J33" s="55" t="s">
+      <c r="I33" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="J33" s="52" t="s">
         <v>190</v>
       </c>
       <c r="K33" s="32">
         <v>3</v>
       </c>
-      <c r="L33" s="55">
+      <c r="L33" s="48">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="M33" s="52">
         <v>100</v>
       </c>
-      <c r="M33" s="32"/>
-    </row>
-    <row r="34" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
+      <c r="N33" s="32"/>
+    </row>
+    <row r="34" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="45"/>
       <c r="B34" s="41">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>240</v>
+      <c r="C34" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>39</v>
@@ -2961,37 +3072,41 @@
       <c r="E34" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="70" t="s">
         <v>149</v>
       </c>
       <c r="H34" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I34" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="J34" s="53" t="s">
+      <c r="I34" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="J34" s="50" t="s">
         <v>191</v>
       </c>
       <c r="K34" s="30">
         <v>8</v>
       </c>
-      <c r="L34" s="53">
+      <c r="L34" s="47">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M34" s="50">
         <v>200</v>
       </c>
-      <c r="M34" s="30"/>
-    </row>
-    <row r="35" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
+      <c r="N34" s="30"/>
+    </row>
+    <row r="35" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45"/>
       <c r="B35" s="41">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>240</v>
+      <c r="C35" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D35" s="32" t="s">
         <v>40</v>
@@ -3009,27 +3124,31 @@
         <v>161</v>
       </c>
       <c r="I35" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="J35" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="J35" s="51" t="s">
         <v>192</v>
       </c>
       <c r="K35" s="32">
         <v>3</v>
       </c>
-      <c r="L35" s="54">
+      <c r="L35" s="32">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="M35" s="51">
         <v>100</v>
       </c>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="N35" s="32"/>
+    </row>
+    <row r="36" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="45"/>
       <c r="B36" s="41">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="60" t="s">
-        <v>240</v>
+      <c r="C36" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D36" s="30" t="s">
         <v>41</v>
@@ -3037,37 +3156,41 @@
       <c r="E36" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="70" t="s">
         <v>151</v>
       </c>
       <c r="H36" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I36" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="J36" s="53" t="s">
+      <c r="I36" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="50" t="s">
         <v>193</v>
       </c>
       <c r="K36" s="30">
         <v>10</v>
       </c>
-      <c r="L36" s="53">
+      <c r="L36" s="47">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="M36" s="50">
         <v>300</v>
       </c>
-      <c r="M36" s="30"/>
-    </row>
-    <row r="37" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="45"/>
       <c r="B37" s="41">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
-        <v>240</v>
+      <c r="C37" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D37" s="32" t="s">
         <v>42</v>
@@ -3085,27 +3208,31 @@
         <v>161</v>
       </c>
       <c r="I37" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="J37" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="J37" s="51" t="s">
         <v>194</v>
       </c>
       <c r="K37" s="32">
         <v>2</v>
       </c>
-      <c r="L37" s="54">
+      <c r="L37" s="32">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="M37" s="51">
         <v>100</v>
       </c>
-      <c r="M37" s="32"/>
-    </row>
-    <row r="38" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="N37" s="32"/>
+    </row>
+    <row r="38" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="45"/>
       <c r="B38" s="41">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
-        <v>240</v>
+      <c r="C38" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>43</v>
@@ -3113,37 +3240,41 @@
       <c r="E38" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="50" t="s">
+      <c r="F38" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="70" t="s">
         <v>153</v>
       </c>
       <c r="H38" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I38" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="J38" s="53" t="s">
+      <c r="I38" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J38" s="50" t="s">
         <v>195</v>
       </c>
       <c r="K38" s="30">
         <v>17</v>
       </c>
-      <c r="L38" s="53">
+      <c r="L38" s="47">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="M38" s="50">
         <v>400</v>
       </c>
-      <c r="M38" s="30"/>
-    </row>
-    <row r="39" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="N38" s="30"/>
+    </row>
+    <row r="39" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="45"/>
       <c r="B39" s="41">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>240</v>
+      <c r="C39" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D39" s="32" t="s">
         <v>44</v>
@@ -3161,63 +3292,71 @@
         <v>161</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="J39" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="J39" s="51" t="s">
         <v>196</v>
       </c>
       <c r="K39" s="32">
         <v>4</v>
       </c>
-      <c r="L39" s="54">
+      <c r="L39" s="32">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="M39" s="51">
         <v>100</v>
       </c>
-      <c r="M39" s="32"/>
-    </row>
-    <row r="40" spans="1:13" s="49" customFormat="1" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="N39" s="32"/>
+    </row>
+    <row r="40" spans="1:14" s="46" customFormat="1" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="45"/>
       <c r="B40" s="41">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" s="59" t="s">
+      <c r="F40" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J40" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K40" s="56">
+      <c r="H40" s="49"/>
+      <c r="I40" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J40" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K40" s="53">
         <v>106</v>
       </c>
-      <c r="L40" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="M40" s="52"/>
-    </row>
-    <row r="41" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="L40" s="53">
+        <f t="shared" si="1"/>
+        <v>2120</v>
+      </c>
+      <c r="M40" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="N40" s="49"/>
+    </row>
+    <row r="41" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="45"/>
       <c r="B41" s="41">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
-        <v>242</v>
+      <c r="C41" s="58" t="s">
+        <v>241</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>46</v>
@@ -3226,7 +3365,7 @@
         <v>89</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>119</v>
@@ -3235,26 +3374,30 @@
         <v>169</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J41" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J41" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K41" s="32">
         <v>1</v>
       </c>
-      <c r="L41" s="54">
+      <c r="L41" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M41" s="51">
         <v>22</v>
       </c>
-      <c r="M41" s="32"/>
-    </row>
-    <row r="42" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="N41" s="32"/>
+    </row>
+    <row r="42" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="45"/>
       <c r="B42" s="41">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="57" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="30" t="s">
@@ -3263,36 +3406,40 @@
       <c r="E42" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F42" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G42" s="73" t="s">
+      <c r="F42" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="70" t="s">
         <v>120</v>
       </c>
       <c r="H42" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="I42" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>201</v>
+      <c r="I42" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="J42" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K42" s="30">
         <v>1</v>
       </c>
-      <c r="L42" s="53">
+      <c r="L42" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M42" s="50">
         <v>22</v>
       </c>
-      <c r="M42" s="30"/>
-    </row>
-    <row r="43" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="45"/>
       <c r="B43" s="41">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="32" t="s">
@@ -3311,26 +3458,30 @@
         <v>167</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="J43" s="54" t="s">
-        <v>201</v>
+        <v>230</v>
+      </c>
+      <c r="J43" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K43" s="32">
         <v>8</v>
       </c>
-      <c r="L43" s="54">
+      <c r="L43" s="32">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="M43" s="51">
         <v>165</v>
       </c>
-      <c r="M43" s="32"/>
-    </row>
-    <row r="44" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="N43" s="32"/>
+    </row>
+    <row r="44" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="45"/>
       <c r="B44" s="41">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="30" t="s">
@@ -3339,36 +3490,40 @@
       <c r="E44" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="50" t="s">
+      <c r="F44" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="73" t="s">
+      <c r="G44" s="70" t="s">
         <v>156</v>
       </c>
       <c r="H44" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="I44" s="50" t="s">
-        <v>232</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>201</v>
+      <c r="I44" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="J44" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K44" s="30">
         <v>1</v>
       </c>
-      <c r="L44" s="53">
+      <c r="L44" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M44" s="50">
         <v>22</v>
       </c>
-      <c r="M44" s="30"/>
-    </row>
-    <row r="45" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="N44" s="30"/>
+    </row>
+    <row r="45" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="45"/>
       <c r="B45" s="41">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="32" t="s">
@@ -3387,24 +3542,28 @@
         <v>167</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="54" t="s">
-        <v>201</v>
+      <c r="J45" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K45" s="32">
         <v>1</v>
       </c>
-      <c r="L45" s="54">
+      <c r="L45" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M45" s="51">
         <v>22</v>
       </c>
-      <c r="M45" s="32"/>
-    </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="N45" s="32"/>
+    </row>
+    <row r="46" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="45"/>
       <c r="B46" s="41">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="30" t="s">
@@ -3413,36 +3572,40 @@
       <c r="E46" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="50" t="s">
-        <v>246</v>
-      </c>
-      <c r="G46" s="73" t="s">
+      <c r="F46" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="G46" s="70" t="s">
         <v>124</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I46" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="J46" s="53" t="s">
-        <v>201</v>
+      <c r="I46" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K46" s="30">
         <v>2</v>
       </c>
-      <c r="L46" s="53">
+      <c r="L46" s="47">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="M46" s="50">
         <v>42</v>
       </c>
-      <c r="M46" s="30"/>
-    </row>
-    <row r="47" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
+      <c r="N46" s="30"/>
+    </row>
+    <row r="47" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="45"/>
       <c r="B47" s="41">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="32" t="s">
@@ -3452,7 +3615,7 @@
         <v>95</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G47" s="33" t="s">
         <v>125</v>
@@ -3461,26 +3624,30 @@
         <v>174</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="J47" s="54" t="s">
-        <v>201</v>
+        <v>233</v>
+      </c>
+      <c r="J47" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K47" s="32">
         <v>1</v>
       </c>
-      <c r="L47" s="54">
+      <c r="L47" s="32">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M47" s="51">
         <v>30</v>
       </c>
-      <c r="M47" s="32"/>
-    </row>
-    <row r="48" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+      <c r="N47" s="32"/>
+    </row>
+    <row r="48" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="45"/>
       <c r="B48" s="41">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="30" t="s">
@@ -3489,34 +3656,38 @@
       <c r="E48" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="F48" s="50" t="s">
+      <c r="F48" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="G48" s="73" t="s">
+      <c r="G48" s="70" t="s">
         <v>158</v>
       </c>
       <c r="H48" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="50"/>
-      <c r="J48" s="53" t="s">
-        <v>201</v>
+      <c r="I48" s="47"/>
+      <c r="J48" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K48" s="30">
         <v>1</v>
       </c>
-      <c r="L48" s="53">
+      <c r="L48" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M48" s="50">
         <v>22</v>
       </c>
-      <c r="M48" s="30"/>
-    </row>
-    <row r="49" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
+      <c r="N48" s="30"/>
+    </row>
+    <row r="49" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="45"/>
       <c r="B49" s="41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="32" t="s">
@@ -3535,25 +3706,29 @@
         <v>175</v>
       </c>
       <c r="I49" s="32"/>
-      <c r="J49" s="54" t="s">
-        <v>201</v>
+      <c r="J49" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K49" s="32">
         <v>4</v>
       </c>
-      <c r="L49" s="54">
+      <c r="L49" s="32">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="M49" s="51">
         <v>82</v>
       </c>
-      <c r="M49" s="32"/>
-    </row>
-    <row r="50" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
+      <c r="N49" s="32"/>
+    </row>
+    <row r="50" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="45"/>
       <c r="B50" s="41">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="60" t="s">
-        <v>243</v>
+      <c r="C50" s="57" t="s">
+        <v>242</v>
       </c>
       <c r="D50" s="30" t="s">
         <v>55</v>
@@ -3561,37 +3736,41 @@
       <c r="E50" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G50" s="73" t="s">
+      <c r="F50" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="70" t="s">
         <v>128</v>
       </c>
       <c r="H50" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="I50" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="J50" s="53" t="s">
-        <v>249</v>
+      <c r="I50" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="J50" s="50" t="s">
+        <v>248</v>
       </c>
       <c r="K50" s="30">
         <v>1</v>
       </c>
-      <c r="L50" s="53">
+      <c r="L50" s="47">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M50" s="50">
         <v>22</v>
       </c>
-      <c r="M50" s="30"/>
-    </row>
-    <row r="51" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
+      <c r="N50" s="30"/>
+    </row>
+    <row r="51" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="45"/>
       <c r="B51" s="41">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
-        <v>243</v>
+      <c r="C51" s="58" t="s">
+        <v>242</v>
       </c>
       <c r="D51" s="32" t="s">
         <v>56</v>
@@ -3599,8 +3778,8 @@
       <c r="E51" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="57" t="s">
-        <v>245</v>
+      <c r="F51" s="54" t="s">
+        <v>244</v>
       </c>
       <c r="G51" s="33" t="s">
         <v>129</v>
@@ -3609,20 +3788,24 @@
         <v>177</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="J51" s="54" t="s">
-        <v>250</v>
+        <v>235</v>
+      </c>
+      <c r="J51" s="51" t="s">
+        <v>249</v>
       </c>
       <c r="K51" s="32">
         <v>2</v>
       </c>
-      <c r="L51" s="54">
+      <c r="L51" s="32">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="M51" s="51">
         <v>45</v>
       </c>
-      <c r="M51" s="57"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="54"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="25"/>
       <c r="C52" s="39"/>
@@ -3635,9 +3818,10 @@
       <c r="J52" s="29"/>
       <c r="K52" s="29"/>
       <c r="L52" s="29"/>
-      <c r="M52" s="35"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="29"/>
+      <c r="N52" s="35"/>
+    </row>
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="20"/>
       <c r="C53" s="40"/>
@@ -3650,12 +3834,13 @@
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="36"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N3:N8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3665,23 +3850,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB907CA-5A05-471D-8486-1FE00697EF7B}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3691,12 +3877,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-    </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="16"/>
       <c r="C2" s="37"/>
@@ -3713,35 +3900,37 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="3"/>
+      <c r="N2" s="34"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="65" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="46"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G3" s="61"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="73"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="17"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="64" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="43" t="s">
         <v>6</v>
       </c>
@@ -3751,16 +3940,17 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="47"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="5"/>
+      <c r="N4" s="74"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="44" t="s">
         <v>7</v>
       </c>
@@ -3770,9 +3960,10 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="47"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="4"/>
+      <c r="N5" s="74"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="18"/>
       <c r="C6" s="38"/>
@@ -3785,39 +3976,42 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="47"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="4"/>
+      <c r="N6" s="74"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="47"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="74"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="47"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="74"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
@@ -3841,28 +4035,31 @@
         <v>160</v>
       </c>
       <c r="I9" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>199</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
+      <c r="L9" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="45"/>
       <c r="B10" s="41">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="30" t="s">
@@ -3871,36 +4068,39 @@
       <c r="E10" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="70" t="s">
         <v>131</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="J10" s="53" t="s">
+      <c r="I10" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="J10" s="50" t="s">
         <v>178</v>
       </c>
       <c r="K10" s="30">
+        <v>20</v>
+      </c>
+      <c r="L10" s="30">
         <v>20000</v>
       </c>
-      <c r="L10" s="53">
+      <c r="M10" s="50">
         <v>20100</v>
       </c>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
+      <c r="N10" s="30"/>
+    </row>
+    <row r="11" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B51" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="32" t="s">
@@ -3919,26 +4119,29 @@
         <v>162</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="J11" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="J11" s="51" t="s">
         <v>179</v>
       </c>
       <c r="K11" s="32">
+        <v>1</v>
+      </c>
+      <c r="L11" s="32">
         <v>1000</v>
       </c>
-      <c r="L11" s="54">
+      <c r="M11" s="51">
         <v>1040</v>
       </c>
-      <c r="M11" s="32"/>
-    </row>
-    <row r="12" spans="1:13" s="49" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" spans="1:14" s="46" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="45"/>
       <c r="B12" s="41">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -3947,36 +4150,39 @@
       <c r="E12" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="70" t="s">
         <v>133</v>
       </c>
       <c r="H12" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I12" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="J12" s="53" t="s">
+      <c r="I12" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="J12" s="50" t="s">
         <v>180</v>
       </c>
       <c r="K12" s="30">
+        <v>43</v>
+      </c>
+      <c r="L12" s="30">
         <v>43000</v>
       </c>
-      <c r="L12" s="53">
+      <c r="M12" s="50">
         <v>43100</v>
       </c>
-      <c r="M12" s="30"/>
-    </row>
-    <row r="13" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
+      <c r="N12" s="30"/>
+    </row>
+    <row r="13" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="45"/>
       <c r="B13" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -3995,26 +4201,29 @@
         <v>161</v>
       </c>
       <c r="I13" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>181</v>
       </c>
       <c r="K13" s="32">
+        <v>12</v>
+      </c>
+      <c r="L13" s="32">
         <v>12000</v>
       </c>
-      <c r="L13" s="54">
+      <c r="M13" s="51">
         <v>12100</v>
       </c>
-      <c r="M13" s="32"/>
-    </row>
-    <row r="14" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="45"/>
       <c r="B14" s="41">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -4023,36 +4232,39 @@
       <c r="E14" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="70" t="s">
         <v>135</v>
       </c>
       <c r="H14" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="I14" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" s="53" t="s">
+      <c r="I14" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="50" t="s">
         <v>182</v>
       </c>
       <c r="K14" s="30">
+        <v>2</v>
+      </c>
+      <c r="L14" s="30">
         <v>2000</v>
       </c>
-      <c r="L14" s="53">
+      <c r="M14" s="50">
         <v>2020</v>
       </c>
-      <c r="M14" s="30"/>
-    </row>
-    <row r="15" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
+      <c r="N14" s="30"/>
+    </row>
+    <row r="15" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="45"/>
       <c r="B15" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -4064,33 +4276,36 @@
       <c r="F15" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="71" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>161</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="J15" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J15" s="51" t="s">
         <v>183</v>
       </c>
       <c r="K15" s="32">
+        <v>16</v>
+      </c>
+      <c r="L15" s="32">
         <v>16000</v>
       </c>
-      <c r="L15" s="54">
+      <c r="M15" s="51">
         <v>16100</v>
       </c>
-      <c r="M15" s="32"/>
-    </row>
-    <row r="16" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="45"/>
       <c r="B16" s="41">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -4099,36 +4314,39 @@
       <c r="E16" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="70" t="s">
         <v>137</v>
       </c>
       <c r="H16" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="J16" s="53" t="s">
+      <c r="I16" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="50" t="s">
         <v>184</v>
       </c>
       <c r="K16" s="30">
+        <v>1</v>
+      </c>
+      <c r="L16" s="30">
         <v>1000</v>
       </c>
-      <c r="L16" s="53">
+      <c r="M16" s="50">
         <v>1020</v>
       </c>
-      <c r="M16" s="30"/>
-    </row>
-    <row r="17" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
+      <c r="N16" s="30"/>
+    </row>
+    <row r="17" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="45"/>
       <c r="B17" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="32" t="s">
@@ -4147,26 +4365,29 @@
         <v>161</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="J17" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" s="51" t="s">
         <v>185</v>
       </c>
       <c r="K17" s="32">
+        <v>6</v>
+      </c>
+      <c r="L17" s="32">
         <v>6000</v>
       </c>
-      <c r="L17" s="54">
+      <c r="M17" s="51">
         <v>6100</v>
       </c>
-      <c r="M17" s="32"/>
-    </row>
-    <row r="18" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+      <c r="N17" s="32"/>
+    </row>
+    <row r="18" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
       <c r="B18" s="41">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="30" t="s">
@@ -4175,36 +4396,39 @@
       <c r="E18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="56" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="I18" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="J18" s="53" t="s">
+      <c r="I18" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K18" s="30">
+        <v>7</v>
+      </c>
+      <c r="L18" s="30">
         <v>7000</v>
       </c>
-      <c r="L18" s="53">
+      <c r="M18" s="50">
         <v>7100</v>
       </c>
-      <c r="M18" s="30"/>
-    </row>
-    <row r="19" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
+      <c r="N18" s="30"/>
+    </row>
+    <row r="19" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="45"/>
       <c r="B19" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="32" t="s">
@@ -4223,26 +4447,29 @@
         <v>161</v>
       </c>
       <c r="I19" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="J19" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="J19" s="51" t="s">
         <v>187</v>
       </c>
       <c r="K19" s="32">
+        <v>4</v>
+      </c>
+      <c r="L19" s="32">
         <v>4000</v>
       </c>
-      <c r="L19" s="54">
+      <c r="M19" s="51">
         <v>4100</v>
       </c>
-      <c r="M19" s="32"/>
-    </row>
-    <row r="20" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
+      <c r="N19" s="32"/>
+    </row>
+    <row r="20" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="45"/>
       <c r="B20" s="41">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="30" t="s">
@@ -4251,36 +4478,39 @@
       <c r="E20" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="70" t="s">
         <v>141</v>
       </c>
       <c r="H20" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" s="53" t="s">
+      <c r="I20" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="50" t="s">
         <v>188</v>
       </c>
       <c r="K20" s="30">
+        <v>1</v>
+      </c>
+      <c r="L20" s="30">
         <v>1000</v>
       </c>
-      <c r="L20" s="53">
+      <c r="M20" s="50">
         <v>1100</v>
       </c>
-      <c r="M20" s="30"/>
-    </row>
-    <row r="21" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48"/>
+      <c r="N20" s="30"/>
+    </row>
+    <row r="21" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="45"/>
       <c r="B21" s="41">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="32" t="s">
@@ -4299,26 +4529,29 @@
         <v>161</v>
       </c>
       <c r="I21" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="J21" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="51" t="s">
         <v>189</v>
       </c>
       <c r="K21" s="32">
+        <v>8</v>
+      </c>
+      <c r="L21" s="32">
         <v>8000</v>
       </c>
-      <c r="L21" s="54">
+      <c r="M21" s="51">
         <v>8100</v>
       </c>
-      <c r="M21" s="32"/>
-    </row>
-    <row r="22" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="45"/>
       <c r="B22" s="41">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="30" t="s">
@@ -4327,36 +4560,39 @@
       <c r="E22" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="73" t="s">
+      <c r="G22" s="70" t="s">
         <v>143</v>
       </c>
       <c r="H22" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="J22" s="53" t="s">
+      <c r="I22" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="J22" s="50" t="s">
         <v>183</v>
       </c>
       <c r="K22" s="30">
+        <v>8</v>
+      </c>
+      <c r="L22" s="30">
         <v>8000</v>
       </c>
-      <c r="L22" s="53">
+      <c r="M22" s="50">
         <v>8100</v>
       </c>
-      <c r="M22" s="30"/>
-    </row>
-    <row r="23" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+      <c r="N22" s="30"/>
+    </row>
+    <row r="23" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="45"/>
       <c r="B23" s="41">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="32" t="s">
@@ -4375,26 +4611,29 @@
         <v>164</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="J23" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>186</v>
       </c>
       <c r="K23" s="32">
+        <v>8</v>
+      </c>
+      <c r="L23" s="32">
         <v>8000</v>
       </c>
-      <c r="L23" s="54">
+      <c r="M23" s="51">
         <v>8050</v>
       </c>
-      <c r="M23" s="32"/>
-    </row>
-    <row r="24" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
+      <c r="N23" s="32"/>
+    </row>
+    <row r="24" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="45"/>
       <c r="B24" s="41">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="30" t="s">
@@ -4403,37 +4642,40 @@
       <c r="E24" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="70" t="s">
         <v>145</v>
       </c>
       <c r="H24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I24" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="J24" s="53" t="s">
+      <c r="I24" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="J24" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K24" s="30">
+        <v>4</v>
+      </c>
+      <c r="L24" s="30">
         <v>4000</v>
       </c>
-      <c r="L24" s="53">
+      <c r="M24" s="50">
         <v>4060</v>
       </c>
-      <c r="M24" s="30"/>
-    </row>
-    <row r="25" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
+      <c r="N24" s="30"/>
+    </row>
+    <row r="25" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="45"/>
       <c r="B25" s="41">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
-        <v>237</v>
+      <c r="C25" s="58" t="s">
+        <v>236</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>30</v>
@@ -4442,7 +4684,7 @@
         <v>73</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>107</v>
@@ -4451,27 +4693,30 @@
         <v>166</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="J25" s="54" t="s">
-        <v>201</v>
+        <v>217</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K25" s="32">
+        <v>1</v>
+      </c>
+      <c r="L25" s="32">
         <v>1000</v>
       </c>
-      <c r="L25" s="54">
+      <c r="M25" s="51">
         <v>1030</v>
       </c>
-      <c r="M25" s="32"/>
-    </row>
-    <row r="26" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="45"/>
       <c r="B26" s="41">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>237</v>
+      <c r="C26" s="57" t="s">
+        <v>236</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>31</v>
@@ -4479,37 +4724,40 @@
       <c r="E26" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="73" t="s">
+      <c r="G26" s="70" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I26" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>201</v>
+      <c r="I26" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="J26" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K26" s="30">
+        <v>1</v>
+      </c>
+      <c r="L26" s="30">
         <v>1000</v>
       </c>
-      <c r="L26" s="53">
+      <c r="M26" s="50">
         <v>1030</v>
       </c>
-      <c r="M26" s="30"/>
-    </row>
-    <row r="27" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
+      <c r="N26" s="30"/>
+    </row>
+    <row r="27" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
       <c r="B27" s="41">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>238</v>
+      <c r="C27" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D27" s="32" t="s">
         <v>32</v>
@@ -4520,33 +4768,36 @@
       <c r="F27" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="74" t="s">
+      <c r="G27" s="71" t="s">
         <v>147</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>168</v>
       </c>
       <c r="I27" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="J27" s="54" t="s">
-        <v>201</v>
+        <v>219</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K27" s="32">
+        <v>1</v>
+      </c>
+      <c r="L27" s="32">
         <v>1000</v>
       </c>
-      <c r="L27" s="54">
+      <c r="M27" s="51">
         <v>1040</v>
       </c>
-      <c r="M27" s="32"/>
-    </row>
-    <row r="28" spans="1:13" s="49" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
+      <c r="N27" s="32"/>
+    </row>
+    <row r="28" spans="1:14" s="46" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
       <c r="B28" s="41">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="57" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="30" t="s">
@@ -4555,36 +4806,39 @@
       <c r="E28" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G28" s="73" t="s">
+      <c r="F28" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="70" t="s">
         <v>110</v>
       </c>
       <c r="H28" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="I28" s="50" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>201</v>
+      <c r="I28" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="J28" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K28" s="30">
+        <v>1</v>
+      </c>
+      <c r="L28" s="30">
         <v>1000</v>
       </c>
-      <c r="L28" s="53">
+      <c r="M28" s="50">
         <v>1020</v>
       </c>
-      <c r="M28" s="30"/>
-    </row>
-    <row r="29" spans="1:13" s="49" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
+      <c r="N28" s="30"/>
+    </row>
+    <row r="29" spans="1:14" s="46" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
       <c r="B29" s="41">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="32" t="s">
@@ -4594,7 +4848,7 @@
         <v>77</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>111</v>
@@ -4603,26 +4857,29 @@
         <v>170</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J29" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K29" s="32">
+        <v>8</v>
+      </c>
+      <c r="L29" s="32">
         <v>8000</v>
       </c>
-      <c r="L29" s="54">
+      <c r="M29" s="51">
         <v>8100</v>
       </c>
-      <c r="M29" s="32"/>
-    </row>
-    <row r="30" spans="1:13" s="49" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
+      <c r="N29" s="32"/>
+    </row>
+    <row r="30" spans="1:14" s="46" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="45"/>
       <c r="B30" s="41">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="57" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="30" t="s">
@@ -4631,33 +4888,36 @@
       <c r="E30" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" s="73" t="s">
+      <c r="F30" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G30" s="70" t="s">
         <v>112</v>
       </c>
       <c r="H30" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="50"/>
-      <c r="J30" s="53" t="s">
-        <v>201</v>
+      <c r="I30" s="47"/>
+      <c r="J30" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K30" s="30">
+        <v>4</v>
+      </c>
+      <c r="L30" s="30">
         <v>4000</v>
       </c>
-      <c r="L30" s="53"/>
-      <c r="M30" s="30"/>
-    </row>
-    <row r="31" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="30"/>
+    </row>
+    <row r="31" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="45"/>
       <c r="B31" s="41">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
-        <v>238</v>
+      <c r="C31" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>36</v>
@@ -4668,72 +4928,78 @@
       <c r="F31" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="74">
+      <c r="G31" s="71">
         <v>61300611121</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>171</v>
       </c>
       <c r="I31" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="J31" s="54" t="s">
-        <v>201</v>
+        <v>221</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K31" s="32">
+        <v>1</v>
+      </c>
+      <c r="L31" s="32">
         <v>1000</v>
       </c>
-      <c r="L31" s="54">
+      <c r="M31" s="51">
         <v>1040</v>
       </c>
-      <c r="M31" s="32"/>
-    </row>
-    <row r="32" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="48"/>
+      <c r="N31" s="32"/>
+    </row>
+    <row r="32" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
       <c r="B32" s="41">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="C32" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G32" s="59" t="s">
+      <c r="F32" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="I32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J32" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K32" s="56">
+      <c r="H32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="53">
+        <v>5</v>
+      </c>
+      <c r="L32" s="53">
         <v>5000</v>
       </c>
-      <c r="L32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="M32" s="52"/>
-    </row>
-    <row r="33" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
+      <c r="M32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="N32" s="49"/>
+    </row>
+    <row r="33" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="45"/>
       <c r="B33" s="41">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>240</v>
+      <c r="C33" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D33" s="32" t="s">
         <v>38</v>
@@ -4744,34 +5010,37 @@
       <c r="F33" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="74" t="s">
+      <c r="G33" s="71" t="s">
         <v>148</v>
       </c>
       <c r="H33" s="32" t="s">
         <v>168</v>
       </c>
       <c r="I33" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="J33" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="J33" s="52" t="s">
         <v>190</v>
       </c>
       <c r="K33" s="32">
+        <v>3</v>
+      </c>
+      <c r="L33" s="32">
         <v>3000</v>
       </c>
-      <c r="L33" s="54">
+      <c r="M33" s="51">
         <v>3100</v>
       </c>
-      <c r="M33" s="32"/>
-    </row>
-    <row r="34" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
+      <c r="N33" s="32"/>
+    </row>
+    <row r="34" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="45"/>
       <c r="B34" s="41">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>240</v>
+      <c r="C34" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>39</v>
@@ -4779,37 +5048,40 @@
       <c r="E34" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="70" t="s">
         <v>149</v>
       </c>
       <c r="H34" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I34" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="J34" s="53" t="s">
+      <c r="I34" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="J34" s="50" t="s">
         <v>191</v>
       </c>
       <c r="K34" s="30">
+        <v>8</v>
+      </c>
+      <c r="L34" s="30">
         <v>8000</v>
       </c>
-      <c r="L34" s="53">
+      <c r="M34" s="50">
         <v>8100</v>
       </c>
-      <c r="M34" s="30"/>
-    </row>
-    <row r="35" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
+      <c r="N34" s="30"/>
+    </row>
+    <row r="35" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45"/>
       <c r="B35" s="41">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>240</v>
+      <c r="C35" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D35" s="32" t="s">
         <v>40</v>
@@ -4827,27 +5099,30 @@
         <v>161</v>
       </c>
       <c r="I35" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="J35" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="J35" s="51" t="s">
         <v>192</v>
       </c>
       <c r="K35" s="32">
+        <v>3</v>
+      </c>
+      <c r="L35" s="32">
         <v>3000</v>
       </c>
-      <c r="L35" s="54">
+      <c r="M35" s="51">
         <v>3100</v>
       </c>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="N35" s="32"/>
+    </row>
+    <row r="36" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="45"/>
       <c r="B36" s="41">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="60" t="s">
-        <v>240</v>
+      <c r="C36" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D36" s="30" t="s">
         <v>41</v>
@@ -4855,37 +5130,40 @@
       <c r="E36" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="70" t="s">
         <v>151</v>
       </c>
       <c r="H36" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I36" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="J36" s="53" t="s">
+      <c r="I36" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="50" t="s">
         <v>193</v>
       </c>
       <c r="K36" s="30">
+        <v>10</v>
+      </c>
+      <c r="L36" s="30">
         <v>10000</v>
       </c>
-      <c r="L36" s="53">
+      <c r="M36" s="50">
         <v>10100</v>
       </c>
-      <c r="M36" s="30"/>
-    </row>
-    <row r="37" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="45"/>
       <c r="B37" s="41">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
-        <v>240</v>
+      <c r="C37" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D37" s="32" t="s">
         <v>42</v>
@@ -4903,27 +5181,30 @@
         <v>161</v>
       </c>
       <c r="I37" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="J37" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="J37" s="51" t="s">
         <v>194</v>
       </c>
       <c r="K37" s="32">
+        <v>2</v>
+      </c>
+      <c r="L37" s="32">
         <v>2000</v>
       </c>
-      <c r="L37" s="54">
+      <c r="M37" s="51">
         <v>2100</v>
       </c>
-      <c r="M37" s="32"/>
-    </row>
-    <row r="38" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="N37" s="32"/>
+    </row>
+    <row r="38" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="45"/>
       <c r="B38" s="41">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
-        <v>240</v>
+      <c r="C38" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>43</v>
@@ -4931,37 +5212,40 @@
       <c r="E38" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="50" t="s">
+      <c r="F38" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="70" t="s">
         <v>153</v>
       </c>
       <c r="H38" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I38" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="J38" s="53" t="s">
+      <c r="I38" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J38" s="50" t="s">
         <v>195</v>
       </c>
       <c r="K38" s="30">
+        <v>17</v>
+      </c>
+      <c r="L38" s="30">
         <v>16000</v>
       </c>
-      <c r="L38" s="53">
+      <c r="M38" s="50">
         <v>16100</v>
       </c>
-      <c r="M38" s="30"/>
-    </row>
-    <row r="39" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="N38" s="30"/>
+    </row>
+    <row r="39" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="45"/>
       <c r="B39" s="41">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>240</v>
+      <c r="C39" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D39" s="32" t="s">
         <v>44</v>
@@ -4979,63 +5263,69 @@
         <v>161</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="J39" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="J39" s="51" t="s">
         <v>196</v>
       </c>
       <c r="K39" s="32">
+        <v>4</v>
+      </c>
+      <c r="L39" s="32">
         <v>4000</v>
       </c>
-      <c r="L39" s="54">
+      <c r="M39" s="51">
         <v>4100</v>
       </c>
-      <c r="M39" s="32"/>
-    </row>
-    <row r="40" spans="1:13" s="49" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="N39" s="32"/>
+    </row>
+    <row r="40" spans="1:14" s="46" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="45"/>
       <c r="B40" s="41">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" s="59" t="s">
+      <c r="F40" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J40" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K40" s="56">
+      <c r="H40" s="49"/>
+      <c r="I40" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J40" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K40" s="53">
+        <v>106</v>
+      </c>
+      <c r="L40" s="53">
         <v>106000</v>
       </c>
-      <c r="L40" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="M40" s="52"/>
-    </row>
-    <row r="41" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="M40" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="N40" s="49"/>
+    </row>
+    <row r="41" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="45"/>
       <c r="B41" s="41">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
-        <v>242</v>
+      <c r="C41" s="58" t="s">
+        <v>241</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>46</v>
@@ -5044,7 +5334,7 @@
         <v>89</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>119</v>
@@ -5053,26 +5343,29 @@
         <v>169</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J41" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J41" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K41" s="32">
+        <v>1</v>
+      </c>
+      <c r="L41" s="32">
         <v>1000</v>
       </c>
-      <c r="L41" s="54">
+      <c r="M41" s="51">
         <v>1050</v>
       </c>
-      <c r="M41" s="32"/>
-    </row>
-    <row r="42" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="N41" s="32"/>
+    </row>
+    <row r="42" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="45"/>
       <c r="B42" s="41">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="57" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="30" t="s">
@@ -5081,36 +5374,39 @@
       <c r="E42" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F42" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G42" s="73" t="s">
+      <c r="F42" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="70" t="s">
         <v>120</v>
       </c>
       <c r="H42" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="I42" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>201</v>
+      <c r="I42" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="J42" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K42" s="30">
+        <v>1</v>
+      </c>
+      <c r="L42" s="30">
         <v>1000</v>
       </c>
-      <c r="L42" s="53">
+      <c r="M42" s="50">
         <v>1020</v>
       </c>
-      <c r="M42" s="30"/>
-    </row>
-    <row r="43" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="45"/>
       <c r="B43" s="41">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="32" t="s">
@@ -5129,24 +5425,27 @@
         <v>167</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="J43" s="54" t="s">
-        <v>201</v>
+        <v>230</v>
+      </c>
+      <c r="J43" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K43" s="32">
+        <v>8</v>
+      </c>
+      <c r="L43" s="32">
         <v>8000</v>
       </c>
-      <c r="L43" s="54"/>
-      <c r="M43" s="32"/>
-    </row>
-    <row r="44" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="32"/>
+    </row>
+    <row r="44" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="45"/>
       <c r="B44" s="41">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="30" t="s">
@@ -5155,36 +5454,39 @@
       <c r="E44" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="50" t="s">
+      <c r="F44" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="73" t="s">
+      <c r="G44" s="70" t="s">
         <v>156</v>
       </c>
       <c r="H44" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="I44" s="50" t="s">
-        <v>232</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>201</v>
+      <c r="I44" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="J44" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K44" s="30">
+        <v>1</v>
+      </c>
+      <c r="L44" s="30">
         <v>1000</v>
       </c>
-      <c r="L44" s="53">
+      <c r="M44" s="50">
         <v>1020</v>
       </c>
-      <c r="M44" s="30"/>
-    </row>
-    <row r="45" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="N44" s="30"/>
+    </row>
+    <row r="45" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="45"/>
       <c r="B45" s="41">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="32" t="s">
@@ -5203,24 +5505,27 @@
         <v>167</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="54" t="s">
-        <v>201</v>
+      <c r="J45" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K45" s="32">
+        <v>1</v>
+      </c>
+      <c r="L45" s="32">
         <v>1000</v>
       </c>
-      <c r="L45" s="54">
+      <c r="M45" s="51">
         <v>1020</v>
       </c>
-      <c r="M45" s="32"/>
-    </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="N45" s="32"/>
+    </row>
+    <row r="46" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="45"/>
       <c r="B46" s="41">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="30" t="s">
@@ -5229,36 +5534,39 @@
       <c r="E46" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="50" t="s">
-        <v>246</v>
-      </c>
-      <c r="G46" s="73" t="s">
+      <c r="F46" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="G46" s="70" t="s">
         <v>124</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I46" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="J46" s="53" t="s">
-        <v>201</v>
+      <c r="I46" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K46" s="30">
+        <v>2</v>
+      </c>
+      <c r="L46" s="30">
         <v>2000</v>
       </c>
-      <c r="L46" s="53">
+      <c r="M46" s="50">
         <v>2020</v>
       </c>
-      <c r="M46" s="30"/>
-    </row>
-    <row r="47" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
+      <c r="N46" s="30"/>
+    </row>
+    <row r="47" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="45"/>
       <c r="B47" s="41">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="32" t="s">
@@ -5268,7 +5576,7 @@
         <v>95</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G47" s="33" t="s">
         <v>125</v>
@@ -5277,26 +5585,29 @@
         <v>174</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="J47" s="54" t="s">
-        <v>201</v>
+        <v>233</v>
+      </c>
+      <c r="J47" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K47" s="32">
+        <v>1</v>
+      </c>
+      <c r="L47" s="32">
         <v>1000</v>
       </c>
-      <c r="L47" s="54">
+      <c r="M47" s="51">
         <v>1020</v>
       </c>
-      <c r="M47" s="32"/>
-    </row>
-    <row r="48" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+      <c r="N47" s="32"/>
+    </row>
+    <row r="48" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="45"/>
       <c r="B48" s="41">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="30" t="s">
@@ -5305,32 +5616,35 @@
       <c r="E48" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="F48" s="50" t="s">
+      <c r="F48" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="G48" s="73" t="s">
+      <c r="G48" s="70" t="s">
         <v>158</v>
       </c>
       <c r="H48" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="50"/>
-      <c r="J48" s="53" t="s">
-        <v>201</v>
+      <c r="I48" s="47"/>
+      <c r="J48" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K48" s="30">
+        <v>1</v>
+      </c>
+      <c r="L48" s="30">
         <v>1000</v>
       </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="30"/>
-    </row>
-    <row r="49" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
+      <c r="M48" s="50"/>
+      <c r="N48" s="30"/>
+    </row>
+    <row r="49" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="45"/>
       <c r="B49" s="41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="32" t="s">
@@ -5349,23 +5663,26 @@
         <v>175</v>
       </c>
       <c r="I49" s="32"/>
-      <c r="J49" s="54" t="s">
-        <v>201</v>
+      <c r="J49" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K49" s="32">
+        <v>4</v>
+      </c>
+      <c r="L49" s="32">
         <v>4000</v>
       </c>
-      <c r="L49" s="54"/>
-      <c r="M49" s="32"/>
-    </row>
-    <row r="50" spans="1:13" s="49" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
+      <c r="M49" s="51"/>
+      <c r="N49" s="32"/>
+    </row>
+    <row r="50" spans="1:14" s="46" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="45"/>
       <c r="B50" s="41">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="60" t="s">
-        <v>243</v>
+      <c r="C50" s="57" t="s">
+        <v>242</v>
       </c>
       <c r="D50" s="30" t="s">
         <v>55</v>
@@ -5373,37 +5690,40 @@
       <c r="E50" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G50" s="73" t="s">
+      <c r="F50" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="70" t="s">
         <v>128</v>
       </c>
       <c r="H50" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="I50" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="J50" s="53" t="s">
-        <v>249</v>
+      <c r="I50" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="J50" s="50" t="s">
+        <v>248</v>
       </c>
       <c r="K50" s="30">
+        <v>1</v>
+      </c>
+      <c r="L50" s="30">
         <v>1000</v>
       </c>
-      <c r="L50" s="53">
+      <c r="M50" s="50">
         <v>1020</v>
       </c>
-      <c r="M50" s="30"/>
-    </row>
-    <row r="51" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
+      <c r="N50" s="30"/>
+    </row>
+    <row r="51" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="45"/>
       <c r="B51" s="41">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
-        <v>243</v>
+      <c r="C51" s="58" t="s">
+        <v>242</v>
       </c>
       <c r="D51" s="32" t="s">
         <v>56</v>
@@ -5411,8 +5731,8 @@
       <c r="E51" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="57" t="s">
-        <v>245</v>
+      <c r="F51" s="54" t="s">
+        <v>244</v>
       </c>
       <c r="G51" s="33" t="s">
         <v>129</v>
@@ -5421,20 +5741,23 @@
         <v>177</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="J51" s="54" t="s">
-        <v>250</v>
+        <v>235</v>
+      </c>
+      <c r="J51" s="51" t="s">
+        <v>249</v>
       </c>
       <c r="K51" s="32">
+        <v>2</v>
+      </c>
+      <c r="L51" s="32">
         <v>2000</v>
       </c>
-      <c r="L51" s="54">
+      <c r="M51" s="51">
         <v>2020</v>
       </c>
-      <c r="M51" s="57"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="54"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="25"/>
       <c r="C52" s="39"/>
@@ -5447,9 +5770,10 @@
       <c r="J52" s="29"/>
       <c r="K52" s="29"/>
       <c r="L52" s="29"/>
-      <c r="M52" s="35"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="29"/>
+      <c r="N52" s="35"/>
+    </row>
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="20"/>
       <c r="C53" s="40"/>
@@ -5462,12 +5786,13 @@
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="36"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N3:N8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5476,11 +5801,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E83DC0-10E5-4C94-A2BD-0F815B8D0D48}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
@@ -5488,12 +5813,13 @@
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5503,12 +5829,13 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-    </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+    </row>
+    <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="16"/>
       <c r="C2" s="37"/>
@@ -5525,35 +5852,37 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="3"/>
+      <c r="N2" s="34"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="17"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64" t="s">
+      <c r="C3" s="60"/>
+      <c r="D3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="65" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="64"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="46"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G3" s="61"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="73"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="17"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="64" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="61"/>
       <c r="F4" s="43" t="s">
         <v>6</v>
       </c>
@@ -5563,16 +5892,17 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="47"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="5"/>
+      <c r="N4" s="74"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="17"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="60"/>
+      <c r="D5" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="44" t="s">
         <v>7</v>
       </c>
@@ -5582,9 +5912,10 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="47"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="4"/>
+      <c r="N5" s="74"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="18"/>
       <c r="C6" s="38"/>
@@ -5597,39 +5928,42 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="47"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="4"/>
+      <c r="N6" s="74"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="19"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="47"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="74"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="22"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="47"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="74"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="23" t="s">
         <v>4</v>
@@ -5653,28 +5987,31 @@
         <v>160</v>
       </c>
       <c r="I9" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="J9" s="23" t="s">
-        <v>199</v>
-      </c>
       <c r="K9" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="L9" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
+      <c r="M9" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="45"/>
       <c r="B10" s="41">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="60" t="s">
+      <c r="C10" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="30" t="s">
@@ -5683,36 +6020,39 @@
       <c r="E10" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="70" t="s">
         <v>131</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="J10" s="53" t="s">
+      <c r="I10" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="J10" s="50" t="s">
         <v>178</v>
       </c>
       <c r="K10" s="30">
+        <v>20</v>
+      </c>
+      <c r="L10" s="30">
         <v>100000</v>
       </c>
-      <c r="L10" s="53">
+      <c r="M10" s="50">
         <v>100100</v>
       </c>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
+      <c r="N10" s="30"/>
+    </row>
+    <row r="11" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="45"/>
       <c r="B11" s="41">
         <f t="shared" ref="B11:B51" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="32" t="s">
@@ -5731,26 +6071,29 @@
         <v>162</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="J11" s="54" t="s">
+        <v>203</v>
+      </c>
+      <c r="J11" s="51" t="s">
         <v>179</v>
       </c>
       <c r="K11" s="32">
+        <v>1</v>
+      </c>
+      <c r="L11" s="32">
         <v>5000</v>
       </c>
-      <c r="L11" s="54">
+      <c r="M11" s="51">
         <v>5060</v>
       </c>
-      <c r="M11" s="32"/>
-    </row>
-    <row r="12" spans="1:13" s="49" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" spans="1:14" s="46" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="45"/>
       <c r="B12" s="41">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -5759,36 +6102,39 @@
       <c r="E12" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="70" t="s">
         <v>133</v>
       </c>
       <c r="H12" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I12" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="J12" s="53" t="s">
+      <c r="I12" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="J12" s="50" t="s">
         <v>180</v>
       </c>
       <c r="K12" s="30">
+        <v>43</v>
+      </c>
+      <c r="L12" s="30">
         <v>215000</v>
       </c>
-      <c r="L12" s="53">
+      <c r="M12" s="50">
         <v>215100</v>
       </c>
-      <c r="M12" s="30"/>
-    </row>
-    <row r="13" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
+      <c r="N12" s="30"/>
+    </row>
+    <row r="13" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="45"/>
       <c r="B13" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="32" t="s">
@@ -5807,26 +6153,29 @@
         <v>161</v>
       </c>
       <c r="I13" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>181</v>
       </c>
       <c r="K13" s="32">
+        <v>12</v>
+      </c>
+      <c r="L13" s="32">
         <v>60000</v>
       </c>
-      <c r="L13" s="54">
+      <c r="M13" s="51">
         <v>60100</v>
       </c>
-      <c r="M13" s="32"/>
-    </row>
-    <row r="14" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="45"/>
       <c r="B14" s="41">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="30" t="s">
@@ -5835,36 +6184,39 @@
       <c r="E14" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="G14" s="73" t="s">
+      <c r="G14" s="70" t="s">
         <v>135</v>
       </c>
       <c r="H14" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="I14" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" s="53" t="s">
+      <c r="I14" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="50" t="s">
         <v>182</v>
       </c>
       <c r="K14" s="30">
+        <v>2</v>
+      </c>
+      <c r="L14" s="30">
         <v>10000</v>
       </c>
-      <c r="L14" s="53">
+      <c r="M14" s="50">
         <v>10100</v>
       </c>
-      <c r="M14" s="30"/>
-    </row>
-    <row r="15" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
+      <c r="N14" s="30"/>
+    </row>
+    <row r="15" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="45"/>
       <c r="B15" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="32" t="s">
@@ -5876,33 +6228,36 @@
       <c r="F15" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="71" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>161</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="J15" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J15" s="51" t="s">
         <v>183</v>
       </c>
       <c r="K15" s="32">
+        <v>16</v>
+      </c>
+      <c r="L15" s="32">
         <v>80000</v>
       </c>
-      <c r="L15" s="54">
+      <c r="M15" s="51">
         <v>80100</v>
       </c>
-      <c r="M15" s="32"/>
-    </row>
-    <row r="16" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="45"/>
       <c r="B16" s="41">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -5911,36 +6266,39 @@
       <c r="E16" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="70" t="s">
         <v>137</v>
       </c>
       <c r="H16" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="J16" s="53" t="s">
+      <c r="I16" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="50" t="s">
         <v>184</v>
       </c>
       <c r="K16" s="30">
+        <v>1</v>
+      </c>
+      <c r="L16" s="30">
         <v>5000</v>
       </c>
-      <c r="L16" s="53">
+      <c r="M16" s="50">
         <v>5010</v>
       </c>
-      <c r="M16" s="30"/>
-    </row>
-    <row r="17" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
+      <c r="N16" s="30"/>
+    </row>
+    <row r="17" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="45"/>
       <c r="B17" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="32" t="s">
@@ -5959,26 +6317,29 @@
         <v>161</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="J17" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="J17" s="51" t="s">
         <v>185</v>
       </c>
       <c r="K17" s="32">
+        <v>6</v>
+      </c>
+      <c r="L17" s="32">
         <v>30000</v>
       </c>
-      <c r="L17" s="54">
+      <c r="M17" s="51">
         <v>30100</v>
       </c>
-      <c r="M17" s="32"/>
-    </row>
-    <row r="18" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+      <c r="N17" s="32"/>
+    </row>
+    <row r="18" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45"/>
       <c r="B18" s="41">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="30" t="s">
@@ -5987,36 +6348,39 @@
       <c r="E18" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="56" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="I18" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="J18" s="53" t="s">
+      <c r="I18" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K18" s="30">
+        <v>7</v>
+      </c>
+      <c r="L18" s="30">
         <v>35000</v>
       </c>
-      <c r="L18" s="53">
+      <c r="M18" s="50">
         <v>35100</v>
       </c>
-      <c r="M18" s="30"/>
-    </row>
-    <row r="19" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
+      <c r="N18" s="30"/>
+    </row>
+    <row r="19" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="45"/>
       <c r="B19" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="32" t="s">
@@ -6035,26 +6399,29 @@
         <v>161</v>
       </c>
       <c r="I19" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="J19" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="J19" s="51" t="s">
         <v>187</v>
       </c>
       <c r="K19" s="32">
+        <v>4</v>
+      </c>
+      <c r="L19" s="32">
         <v>20000</v>
       </c>
-      <c r="L19" s="54">
+      <c r="M19" s="51">
         <v>20100</v>
       </c>
-      <c r="M19" s="32"/>
-    </row>
-    <row r="20" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
+      <c r="N19" s="32"/>
+    </row>
+    <row r="20" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="45"/>
       <c r="B20" s="41">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="30" t="s">
@@ -6063,36 +6430,39 @@
       <c r="E20" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="70" t="s">
         <v>141</v>
       </c>
       <c r="H20" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" s="53" t="s">
+      <c r="I20" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="50" t="s">
         <v>188</v>
       </c>
       <c r="K20" s="30">
+        <v>1</v>
+      </c>
+      <c r="L20" s="30">
         <v>5000</v>
       </c>
-      <c r="L20" s="53">
+      <c r="M20" s="50">
         <v>5100</v>
       </c>
-      <c r="M20" s="30"/>
-    </row>
-    <row r="21" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="48"/>
+      <c r="N20" s="30"/>
+    </row>
+    <row r="21" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="45"/>
       <c r="B21" s="41">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="61" t="s">
+      <c r="C21" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="32" t="s">
@@ -6111,26 +6481,29 @@
         <v>161</v>
       </c>
       <c r="I21" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="J21" s="54" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="51" t="s">
         <v>189</v>
       </c>
       <c r="K21" s="32">
+        <v>8</v>
+      </c>
+      <c r="L21" s="32">
         <v>40000</v>
       </c>
-      <c r="L21" s="54">
+      <c r="M21" s="51">
         <v>40100</v>
       </c>
-      <c r="M21" s="32"/>
-    </row>
-    <row r="22" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="45"/>
       <c r="B22" s="41">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="30" t="s">
@@ -6139,36 +6512,39 @@
       <c r="E22" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="73" t="s">
+      <c r="G22" s="70" t="s">
         <v>143</v>
       </c>
       <c r="H22" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="J22" s="53" t="s">
+      <c r="I22" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="J22" s="50" t="s">
         <v>183</v>
       </c>
       <c r="K22" s="30">
+        <v>8</v>
+      </c>
+      <c r="L22" s="30">
         <v>40000</v>
       </c>
-      <c r="L22" s="53">
+      <c r="M22" s="50">
         <v>40100</v>
       </c>
-      <c r="M22" s="30"/>
-    </row>
-    <row r="23" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
+      <c r="N22" s="30"/>
+    </row>
+    <row r="23" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="45"/>
       <c r="B23" s="41">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="61" t="s">
+      <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="32" t="s">
@@ -6187,26 +6563,29 @@
         <v>164</v>
       </c>
       <c r="I23" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="J23" s="54" t="s">
+        <v>215</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>186</v>
       </c>
       <c r="K23" s="32">
+        <v>8</v>
+      </c>
+      <c r="L23" s="32">
         <v>40000</v>
       </c>
-      <c r="L23" s="54">
+      <c r="M23" s="51">
         <v>40100</v>
       </c>
-      <c r="M23" s="32"/>
-    </row>
-    <row r="24" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
+      <c r="N23" s="32"/>
+    </row>
+    <row r="24" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="45"/>
       <c r="B24" s="41">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="57" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="30" t="s">
@@ -6215,37 +6594,40 @@
       <c r="E24" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="70" t="s">
         <v>145</v>
       </c>
       <c r="H24" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I24" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="J24" s="53" t="s">
+      <c r="I24" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="J24" s="50" t="s">
         <v>186</v>
       </c>
       <c r="K24" s="30">
+        <v>4</v>
+      </c>
+      <c r="L24" s="30">
         <v>20000</v>
       </c>
-      <c r="L24" s="53">
+      <c r="M24" s="50">
         <v>20100</v>
       </c>
-      <c r="M24" s="30"/>
-    </row>
-    <row r="25" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
+      <c r="N24" s="30"/>
+    </row>
+    <row r="25" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="45"/>
       <c r="B25" s="41">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="61" t="s">
-        <v>237</v>
+      <c r="C25" s="58" t="s">
+        <v>236</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>30</v>
@@ -6254,7 +6636,7 @@
         <v>73</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G25" s="33" t="s">
         <v>107</v>
@@ -6263,27 +6645,30 @@
         <v>166</v>
       </c>
       <c r="I25" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="J25" s="54" t="s">
-        <v>201</v>
+        <v>217</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K25" s="32">
+        <v>1</v>
+      </c>
+      <c r="L25" s="32">
         <v>5000</v>
       </c>
-      <c r="L25" s="54">
+      <c r="M25" s="51">
         <v>5030</v>
       </c>
-      <c r="M25" s="32"/>
-    </row>
-    <row r="26" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="45"/>
       <c r="B26" s="41">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>237</v>
+      <c r="C26" s="57" t="s">
+        <v>236</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>31</v>
@@ -6291,37 +6676,40 @@
       <c r="E26" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="73" t="s">
+      <c r="G26" s="70" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I26" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>201</v>
+      <c r="I26" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="J26" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K26" s="30">
+        <v>1</v>
+      </c>
+      <c r="L26" s="30">
         <v>5000</v>
       </c>
-      <c r="L26" s="53">
+      <c r="M26" s="50">
         <v>5030</v>
       </c>
-      <c r="M26" s="30"/>
-    </row>
-    <row r="27" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
+      <c r="N26" s="30"/>
+    </row>
+    <row r="27" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
       <c r="B27" s="41">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>238</v>
+      <c r="C27" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D27" s="32" t="s">
         <v>32</v>
@@ -6332,33 +6720,36 @@
       <c r="F27" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="74" t="s">
+      <c r="G27" s="71" t="s">
         <v>147</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>168</v>
       </c>
       <c r="I27" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="J27" s="54" t="s">
-        <v>201</v>
+        <v>219</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K27" s="32">
+        <v>1</v>
+      </c>
+      <c r="L27" s="32">
         <v>5000</v>
       </c>
-      <c r="L27" s="54">
+      <c r="M27" s="51">
         <v>5060</v>
       </c>
-      <c r="M27" s="32"/>
-    </row>
-    <row r="28" spans="1:13" s="49" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
+      <c r="N27" s="32"/>
+    </row>
+    <row r="28" spans="1:14" s="46" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
       <c r="B28" s="41">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="57" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="30" t="s">
@@ -6367,36 +6758,39 @@
       <c r="E28" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G28" s="73" t="s">
+      <c r="F28" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G28" s="70" t="s">
         <v>110</v>
       </c>
       <c r="H28" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="I28" s="50" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>201</v>
+      <c r="I28" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="J28" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K28" s="30">
+        <v>1</v>
+      </c>
+      <c r="L28" s="30">
         <v>5000</v>
       </c>
-      <c r="L28" s="53">
+      <c r="M28" s="50">
         <v>5060</v>
       </c>
-      <c r="M28" s="30"/>
-    </row>
-    <row r="29" spans="1:13" s="49" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
+      <c r="N28" s="30"/>
+    </row>
+    <row r="29" spans="1:14" s="46" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
       <c r="B29" s="41">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="58" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="32" t="s">
@@ -6406,7 +6800,7 @@
         <v>77</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>111</v>
@@ -6415,24 +6809,27 @@
         <v>170</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J29" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K29" s="32">
+        <v>8</v>
+      </c>
+      <c r="L29" s="32">
         <v>40000</v>
       </c>
-      <c r="L29" s="54"/>
-      <c r="M29" s="32"/>
-    </row>
-    <row r="30" spans="1:13" s="49" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="32"/>
+    </row>
+    <row r="30" spans="1:14" s="46" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="45"/>
       <c r="B30" s="41">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="60" t="s">
+      <c r="C30" s="57" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="30" t="s">
@@ -6441,33 +6838,36 @@
       <c r="E30" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F30" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" s="73" t="s">
+      <c r="F30" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G30" s="70" t="s">
         <v>112</v>
       </c>
       <c r="H30" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="50"/>
-      <c r="J30" s="53" t="s">
-        <v>201</v>
+      <c r="I30" s="47"/>
+      <c r="J30" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K30" s="30">
+        <v>4</v>
+      </c>
+      <c r="L30" s="30">
         <v>20000</v>
       </c>
-      <c r="L30" s="53"/>
-      <c r="M30" s="30"/>
-    </row>
-    <row r="31" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="30"/>
+    </row>
+    <row r="31" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="45"/>
       <c r="B31" s="41">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="61" t="s">
-        <v>238</v>
+      <c r="C31" s="58" t="s">
+        <v>237</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>36</v>
@@ -6478,70 +6878,76 @@
       <c r="F31" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="74">
+      <c r="G31" s="71">
         <v>61300611121</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>171</v>
       </c>
       <c r="I31" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="J31" s="54" t="s">
-        <v>201</v>
+        <v>221</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K31" s="32">
+        <v>1</v>
+      </c>
+      <c r="L31" s="32">
         <v>5000</v>
       </c>
-      <c r="L31" s="54">
+      <c r="M31" s="51">
         <v>5060</v>
       </c>
-      <c r="M31" s="32"/>
-    </row>
-    <row r="32" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="48"/>
+      <c r="N31" s="32"/>
+    </row>
+    <row r="32" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
       <c r="B32" s="41">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="58" t="s">
+      <c r="C32" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G32" s="59" t="s">
+      <c r="F32" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G32" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="I32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J32" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K32" s="56">
+      <c r="H32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J32" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="53">
+        <v>5</v>
+      </c>
+      <c r="L32" s="53">
         <v>25000</v>
       </c>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-    </row>
-    <row r="33" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+    </row>
+    <row r="33" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="45"/>
       <c r="B33" s="41">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="61" t="s">
-        <v>240</v>
+      <c r="C33" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D33" s="32" t="s">
         <v>38</v>
@@ -6552,34 +6958,37 @@
       <c r="F33" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="74" t="s">
+      <c r="G33" s="71" t="s">
         <v>148</v>
       </c>
       <c r="H33" s="32" t="s">
         <v>168</v>
       </c>
       <c r="I33" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="J33" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="J33" s="51" t="s">
         <v>190</v>
       </c>
       <c r="K33" s="32">
+        <v>3</v>
+      </c>
+      <c r="L33" s="32">
         <v>15000</v>
       </c>
-      <c r="L33" s="54">
+      <c r="M33" s="51">
         <v>15100</v>
       </c>
-      <c r="M33" s="32"/>
-    </row>
-    <row r="34" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
+      <c r="N33" s="32"/>
+    </row>
+    <row r="34" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="45"/>
       <c r="B34" s="41">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="60" t="s">
-        <v>240</v>
+      <c r="C34" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>39</v>
@@ -6587,37 +6996,40 @@
       <c r="E34" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="70" t="s">
         <v>149</v>
       </c>
       <c r="H34" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I34" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="J34" s="53" t="s">
+      <c r="I34" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="J34" s="50" t="s">
         <v>191</v>
       </c>
       <c r="K34" s="30">
+        <v>8</v>
+      </c>
+      <c r="L34" s="30">
         <v>40000</v>
       </c>
-      <c r="L34" s="53">
+      <c r="M34" s="50">
         <v>40100</v>
       </c>
-      <c r="M34" s="30"/>
-    </row>
-    <row r="35" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
+      <c r="N34" s="30"/>
+    </row>
+    <row r="35" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45"/>
       <c r="B35" s="41">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>240</v>
+      <c r="C35" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D35" s="32" t="s">
         <v>40</v>
@@ -6635,27 +7047,30 @@
         <v>161</v>
       </c>
       <c r="I35" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="J35" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="J35" s="51" t="s">
         <v>192</v>
       </c>
       <c r="K35" s="32">
+        <v>3</v>
+      </c>
+      <c r="L35" s="32">
         <v>15000</v>
       </c>
-      <c r="L35" s="54">
+      <c r="M35" s="51">
         <v>15100</v>
       </c>
-      <c r="M35" s="32"/>
-    </row>
-    <row r="36" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="N35" s="32"/>
+    </row>
+    <row r="36" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="45"/>
       <c r="B36" s="41">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="60" t="s">
-        <v>240</v>
+      <c r="C36" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D36" s="30" t="s">
         <v>41</v>
@@ -6663,37 +7078,40 @@
       <c r="E36" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="70" t="s">
         <v>151</v>
       </c>
       <c r="H36" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I36" s="50" t="s">
-        <v>226</v>
-      </c>
-      <c r="J36" s="53" t="s">
+      <c r="I36" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="50" t="s">
         <v>193</v>
       </c>
       <c r="K36" s="30">
+        <v>10</v>
+      </c>
+      <c r="L36" s="30">
         <v>50000</v>
       </c>
-      <c r="L36" s="53">
+      <c r="M36" s="50">
         <v>50100</v>
       </c>
-      <c r="M36" s="30"/>
-    </row>
-    <row r="37" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="45"/>
       <c r="B37" s="41">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="61" t="s">
-        <v>240</v>
+      <c r="C37" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D37" s="32" t="s">
         <v>42</v>
@@ -6711,27 +7129,30 @@
         <v>161</v>
       </c>
       <c r="I37" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="J37" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="J37" s="51" t="s">
         <v>194</v>
       </c>
       <c r="K37" s="32">
+        <v>2</v>
+      </c>
+      <c r="L37" s="32">
         <v>10000</v>
       </c>
-      <c r="L37" s="54">
+      <c r="M37" s="51">
         <v>10100</v>
       </c>
-      <c r="M37" s="32"/>
-    </row>
-    <row r="38" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
+      <c r="N37" s="32"/>
+    </row>
+    <row r="38" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="45"/>
       <c r="B38" s="41">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="60" t="s">
-        <v>240</v>
+      <c r="C38" s="57" t="s">
+        <v>239</v>
       </c>
       <c r="D38" s="30" t="s">
         <v>43</v>
@@ -6739,37 +7160,40 @@
       <c r="E38" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="50" t="s">
+      <c r="F38" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="73" t="s">
+      <c r="G38" s="70" t="s">
         <v>153</v>
       </c>
       <c r="H38" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I38" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="J38" s="53" t="s">
+      <c r="I38" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J38" s="50" t="s">
         <v>195</v>
       </c>
       <c r="K38" s="30">
+        <v>17</v>
+      </c>
+      <c r="L38" s="30">
         <v>80000</v>
       </c>
-      <c r="L38" s="53">
+      <c r="M38" s="50">
         <v>80100</v>
       </c>
-      <c r="M38" s="30"/>
-    </row>
-    <row r="39" spans="1:13" s="49" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
+      <c r="N38" s="30"/>
+    </row>
+    <row r="39" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="45"/>
       <c r="B39" s="41">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>240</v>
+      <c r="C39" s="58" t="s">
+        <v>239</v>
       </c>
       <c r="D39" s="32" t="s">
         <v>44</v>
@@ -6787,61 +7211,67 @@
         <v>161</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="J39" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="J39" s="51" t="s">
         <v>196</v>
       </c>
       <c r="K39" s="32">
+        <v>4</v>
+      </c>
+      <c r="L39" s="32">
         <v>20000</v>
       </c>
-      <c r="L39" s="54">
+      <c r="M39" s="51">
         <v>20100</v>
       </c>
-      <c r="M39" s="32"/>
-    </row>
-    <row r="40" spans="1:13" s="49" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
+      <c r="N39" s="32"/>
+    </row>
+    <row r="40" spans="1:14" s="46" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="45"/>
       <c r="B40" s="41">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="60" t="s">
-        <v>241</v>
-      </c>
-      <c r="D40" s="58" t="s">
+      <c r="C40" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="52" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" s="59" t="s">
+      <c r="F40" s="49" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="J40" s="56" t="s">
-        <v>201</v>
-      </c>
-      <c r="K40" s="56">
+      <c r="H40" s="49"/>
+      <c r="I40" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="J40" s="53" t="s">
+        <v>200</v>
+      </c>
+      <c r="K40" s="53">
+        <v>106</v>
+      </c>
+      <c r="L40" s="53">
         <v>530000</v>
       </c>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-    </row>
-    <row r="41" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
+      <c r="M40" s="49"/>
+      <c r="N40" s="49"/>
+    </row>
+    <row r="41" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="45"/>
       <c r="B41" s="41">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="61" t="s">
-        <v>242</v>
+      <c r="C41" s="58" t="s">
+        <v>241</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>46</v>
@@ -6850,7 +7280,7 @@
         <v>89</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>119</v>
@@ -6859,26 +7289,29 @@
         <v>169</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="J41" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="J41" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K41" s="32">
+        <v>1</v>
+      </c>
+      <c r="L41" s="32">
         <v>5000</v>
       </c>
-      <c r="L41" s="54">
+      <c r="M41" s="51">
         <v>5050</v>
       </c>
-      <c r="M41" s="32"/>
-    </row>
-    <row r="42" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="N41" s="32"/>
+    </row>
+    <row r="42" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="45"/>
       <c r="B42" s="41">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="57" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="30" t="s">
@@ -6887,36 +7320,39 @@
       <c r="E42" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F42" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G42" s="73" t="s">
+      <c r="F42" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="70" t="s">
         <v>120</v>
       </c>
       <c r="H42" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="I42" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="J42" s="53" t="s">
-        <v>201</v>
+      <c r="I42" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="J42" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K42" s="30">
+        <v>1</v>
+      </c>
+      <c r="L42" s="30">
         <v>5000</v>
       </c>
-      <c r="L42" s="53">
+      <c r="M42" s="50">
         <v>5020</v>
       </c>
-      <c r="M42" s="30"/>
-    </row>
-    <row r="43" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
+      <c r="N42" s="30"/>
+    </row>
+    <row r="43" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="45"/>
       <c r="B43" s="41">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="32" t="s">
@@ -6935,24 +7371,27 @@
         <v>167</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="J43" s="54" t="s">
-        <v>201</v>
+        <v>230</v>
+      </c>
+      <c r="J43" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K43" s="32">
+        <v>8</v>
+      </c>
+      <c r="L43" s="32">
         <v>40000</v>
       </c>
-      <c r="L43" s="54"/>
-      <c r="M43" s="32"/>
-    </row>
-    <row r="44" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="32"/>
+    </row>
+    <row r="44" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="45"/>
       <c r="B44" s="41">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="60" t="s">
+      <c r="C44" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D44" s="30" t="s">
@@ -6961,36 +7400,39 @@
       <c r="E44" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="F44" s="50" t="s">
+      <c r="F44" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="73" t="s">
+      <c r="G44" s="70" t="s">
         <v>156</v>
       </c>
       <c r="H44" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="I44" s="50" t="s">
-        <v>232</v>
-      </c>
-      <c r="J44" s="53" t="s">
-        <v>201</v>
+      <c r="I44" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="J44" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K44" s="30">
+        <v>1</v>
+      </c>
+      <c r="L44" s="30">
         <v>5000</v>
       </c>
-      <c r="L44" s="53">
+      <c r="M44" s="50">
         <v>5020</v>
       </c>
-      <c r="M44" s="30"/>
-    </row>
-    <row r="45" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
+      <c r="N44" s="30"/>
+    </row>
+    <row r="45" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="45"/>
       <c r="B45" s="41">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="32" t="s">
@@ -7009,24 +7451,27 @@
         <v>167</v>
       </c>
       <c r="I45" s="32"/>
-      <c r="J45" s="54" t="s">
-        <v>201</v>
+      <c r="J45" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K45" s="32">
+        <v>1</v>
+      </c>
+      <c r="L45" s="32">
         <v>5000</v>
       </c>
-      <c r="L45" s="54">
+      <c r="M45" s="51">
         <v>5020</v>
       </c>
-      <c r="M45" s="32"/>
-    </row>
-    <row r="46" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
+      <c r="N45" s="32"/>
+    </row>
+    <row r="46" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="45"/>
       <c r="B46" s="41">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="30" t="s">
@@ -7035,36 +7480,39 @@
       <c r="E46" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="50" t="s">
-        <v>246</v>
-      </c>
-      <c r="G46" s="73" t="s">
+      <c r="F46" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="G46" s="70" t="s">
         <v>124</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I46" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="J46" s="53" t="s">
-        <v>201</v>
+      <c r="I46" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="J46" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K46" s="30">
+        <v>2</v>
+      </c>
+      <c r="L46" s="30">
         <v>10000</v>
       </c>
-      <c r="L46" s="53">
+      <c r="M46" s="50">
         <v>10040</v>
       </c>
-      <c r="M46" s="30"/>
-    </row>
-    <row r="47" spans="1:13" s="49" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
+      <c r="N46" s="30"/>
+    </row>
+    <row r="47" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="45"/>
       <c r="B47" s="41">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="32" t="s">
@@ -7074,7 +7522,7 @@
         <v>95</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G47" s="33" t="s">
         <v>125</v>
@@ -7083,26 +7531,29 @@
         <v>174</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="J47" s="54" t="s">
-        <v>201</v>
+        <v>233</v>
+      </c>
+      <c r="J47" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K47" s="32">
+        <v>1</v>
+      </c>
+      <c r="L47" s="32">
         <v>5000</v>
       </c>
-      <c r="L47" s="54">
+      <c r="M47" s="51">
         <v>5020</v>
       </c>
-      <c r="M47" s="32"/>
-    </row>
-    <row r="48" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+      <c r="N47" s="32"/>
+    </row>
+    <row r="48" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="45"/>
       <c r="B48" s="41">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="30" t="s">
@@ -7111,32 +7562,35 @@
       <c r="E48" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="F48" s="50" t="s">
+      <c r="F48" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="G48" s="73" t="s">
+      <c r="G48" s="70" t="s">
         <v>158</v>
       </c>
       <c r="H48" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="50"/>
-      <c r="J48" s="53" t="s">
-        <v>201</v>
+      <c r="I48" s="47"/>
+      <c r="J48" s="50" t="s">
+        <v>200</v>
       </c>
       <c r="K48" s="30">
+        <v>1</v>
+      </c>
+      <c r="L48" s="30">
         <v>5000</v>
       </c>
-      <c r="L48" s="53"/>
-      <c r="M48" s="30"/>
-    </row>
-    <row r="49" spans="1:13" s="49" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
+      <c r="M48" s="50"/>
+      <c r="N48" s="30"/>
+    </row>
+    <row r="49" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="45"/>
       <c r="B49" s="41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="58" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="32" t="s">
@@ -7155,23 +7609,26 @@
         <v>175</v>
       </c>
       <c r="I49" s="32"/>
-      <c r="J49" s="54" t="s">
-        <v>201</v>
+      <c r="J49" s="51" t="s">
+        <v>200</v>
       </c>
       <c r="K49" s="32">
+        <v>4</v>
+      </c>
+      <c r="L49" s="32">
         <v>20000</v>
       </c>
-      <c r="L49" s="54"/>
-      <c r="M49" s="32"/>
-    </row>
-    <row r="50" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
+      <c r="M49" s="51"/>
+      <c r="N49" s="32"/>
+    </row>
+    <row r="50" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="45"/>
       <c r="B50" s="41">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="60" t="s">
-        <v>243</v>
+      <c r="C50" s="57" t="s">
+        <v>242</v>
       </c>
       <c r="D50" s="30" t="s">
         <v>55</v>
@@ -7179,37 +7636,40 @@
       <c r="E50" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="G50" s="73" t="s">
+      <c r="F50" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="70" t="s">
         <v>128</v>
       </c>
       <c r="H50" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="I50" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="J50" s="53" t="s">
-        <v>249</v>
+      <c r="I50" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="J50" s="50" t="s">
+        <v>248</v>
       </c>
       <c r="K50" s="30">
+        <v>1</v>
+      </c>
+      <c r="L50" s="30">
         <v>5000</v>
       </c>
-      <c r="L50" s="53">
+      <c r="M50" s="50">
         <v>5050</v>
       </c>
-      <c r="M50" s="30"/>
-    </row>
-    <row r="51" spans="1:13" s="49" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
+      <c r="N50" s="30"/>
+    </row>
+    <row r="51" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="45"/>
       <c r="B51" s="41">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="61" t="s">
-        <v>243</v>
+      <c r="C51" s="58" t="s">
+        <v>242</v>
       </c>
       <c r="D51" s="32" t="s">
         <v>56</v>
@@ -7217,8 +7677,8 @@
       <c r="E51" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="57" t="s">
-        <v>245</v>
+      <c r="F51" s="54" t="s">
+        <v>244</v>
       </c>
       <c r="G51" s="33" t="s">
         <v>129</v>
@@ -7227,20 +7687,23 @@
         <v>177</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="J51" s="54" t="s">
-        <v>250</v>
+        <v>235</v>
+      </c>
+      <c r="J51" s="51" t="s">
+        <v>249</v>
       </c>
       <c r="K51" s="32">
+        <v>2</v>
+      </c>
+      <c r="L51" s="32">
         <v>10000</v>
       </c>
-      <c r="L51" s="54">
+      <c r="M51" s="51">
         <v>10050</v>
       </c>
-      <c r="M51" s="57"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N51" s="54"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="25"/>
       <c r="C52" s="39"/>
@@ -7253,9 +7716,10 @@
       <c r="J52" s="29"/>
       <c r="K52" s="29"/>
       <c r="L52" s="29"/>
-      <c r="M52" s="35"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="29"/>
+      <c r="N52" s="35"/>
+    </row>
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="20"/>
       <c r="C53" s="40"/>
@@ -7268,12 +7732,13 @@
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="36"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="N3:N8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Deliverables/BOM/PCBWay-BOM_20.pcs.xlsx
+++ b/Deliverables/BOM/PCBWay-BOM_20.pcs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Melih-SoundSensor\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E114134-175D-4FE0-AF94-AAFB86D1296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5054272F-2742-4952-8E0A-841E626F85CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,11 +18,24 @@
     <sheet name="5K Boards" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="266">
   <si>
     <t>Component list</t>
   </si>
@@ -787,6 +800,40 @@
   </si>
   <si>
     <t>Quantity (20 Boards)</t>
+  </si>
+  <si>
+    <t>R15, R16, R17,  R18, R19, R20, R21, R28, R29, R30, R31, R32, R33, R36, R37, R40, R41</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>C318893</t>
+  </si>
+  <si>
+    <t>C123008</t>
+  </si>
+  <si>
+    <t>CL10B104KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1608X5R1E106MT000E</t>
+  </si>
+  <si>
+    <t>PZ254V-11-05P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS-03K104JT
+</t>
+  </si>
+  <si>
+    <t>UMH3NTN</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [Sound_Sensor}</t>
+  </si>
+  <si>
+    <t>Sound_Sensor</t>
   </si>
 </sst>
 </file>
@@ -796,7 +843,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -935,6 +982,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -968,7 +1022,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1191,11 +1245,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1399,6 +1479,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1892,7 +1993,7 @@
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="42" t="s">
-        <v>5</v>
+        <v>264</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="3"/>
@@ -1912,7 +2013,7 @@
       </c>
       <c r="E3" s="61"/>
       <c r="F3" s="62" t="s">
-        <v>6</v>
+        <v>265</v>
       </c>
       <c r="G3" s="61"/>
       <c r="H3" s="63"/>
@@ -1932,7 +2033,7 @@
       </c>
       <c r="E4" s="61"/>
       <c r="F4" s="43" t="s">
-        <v>6</v>
+        <v>265</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="5"/>
@@ -2013,35 +2114,35 @@
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="24" t="s">
         <v>100</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="24" t="s">
         <v>160</v>
       </c>
-      <c r="I9" s="24" t="s">
+      <c r="I9" s="23" t="s">
         <v>197</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>198</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>254</v>
@@ -2062,10 +2163,10 @@
       <c r="C10" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="70" t="s">
         <v>58</v>
       </c>
       <c r="F10" s="47" t="s">
@@ -2074,7 +2175,7 @@
       <c r="G10" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I10" s="47" t="s">
@@ -2083,7 +2184,7 @@
       <c r="J10" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="47">
         <v>20</v>
       </c>
       <c r="L10" s="47">
@@ -2098,16 +2199,16 @@
     <row r="11" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="45"/>
       <c r="B11" s="41">
-        <f t="shared" ref="B11:B51" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B50" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="32" t="s">
         <v>59</v>
       </c>
       <c r="F11" s="32" t="s">
@@ -2125,7 +2226,7 @@
       <c r="J11" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="K11" s="32">
+      <c r="K11" s="80">
         <v>1</v>
       </c>
       <c r="L11" s="32">
@@ -2146,10 +2247,10 @@
       <c r="C12" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="70" t="s">
         <v>60</v>
       </c>
       <c r="F12" s="47" t="s">
@@ -2158,7 +2259,7 @@
       <c r="G12" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I12" s="47" t="s">
@@ -2167,7 +2268,7 @@
       <c r="J12" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="47">
         <v>43</v>
       </c>
       <c r="L12" s="47">
@@ -2188,10 +2289,10 @@
       <c r="C13" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="32" t="s">
         <v>61</v>
       </c>
       <c r="F13" s="32" t="s">
@@ -2209,7 +2310,7 @@
       <c r="J13" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="80">
         <v>12</v>
       </c>
       <c r="L13" s="32">
@@ -2230,10 +2331,10 @@
       <c r="C14" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="70" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="47" t="s">
@@ -2242,7 +2343,7 @@
       <c r="G14" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="47" t="s">
         <v>163</v>
       </c>
       <c r="I14" s="47" t="s">
@@ -2251,7 +2352,7 @@
       <c r="J14" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="47">
         <v>2</v>
       </c>
       <c r="L14" s="47">
@@ -2266,23 +2367,23 @@
     <row r="15" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="45"/>
       <c r="B15" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
       <c r="C15" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="71" t="s">
-        <v>136</v>
+      <c r="G15" s="32" t="s">
+        <v>259</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>161</v>
@@ -2293,7 +2394,7 @@
       <c r="J15" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="80">
         <v>16</v>
       </c>
       <c r="L15" s="32">
@@ -2308,16 +2409,16 @@
     <row r="16" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45"/>
       <c r="B16" s="41">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="70" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="47" t="s">
@@ -2326,7 +2427,7 @@
       <c r="G16" s="70" t="s">
         <v>137</v>
       </c>
-      <c r="H16" s="30" t="s">
+      <c r="H16" s="47" t="s">
         <v>164</v>
       </c>
       <c r="I16" s="47" t="s">
@@ -2335,7 +2436,7 @@
       <c r="J16" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="47">
         <v>1</v>
       </c>
       <c r="L16" s="47">
@@ -2350,16 +2451,16 @@
     <row r="17" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="45"/>
       <c r="B17" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
       <c r="C17" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="32" t="s">
         <v>65</v>
       </c>
       <c r="F17" s="32" t="s">
@@ -2377,7 +2478,7 @@
       <c r="J17" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="80">
         <v>6</v>
       </c>
       <c r="L17" s="32">
@@ -2398,19 +2499,19 @@
       <c r="C18" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="70" t="s">
         <v>66</v>
       </c>
       <c r="F18" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="H18" s="30" t="s">
+      <c r="G18" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="H18" s="47" t="s">
         <v>165</v>
       </c>
       <c r="I18" s="47" t="s">
@@ -2419,7 +2520,7 @@
       <c r="J18" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="47">
         <v>7</v>
       </c>
       <c r="L18" s="47">
@@ -2434,16 +2535,16 @@
     <row r="19" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45"/>
       <c r="B19" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
       <c r="C19" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="32" t="s">
         <v>67</v>
       </c>
       <c r="F19" s="32" t="s">
@@ -2461,7 +2562,7 @@
       <c r="J19" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="80">
         <v>4</v>
       </c>
       <c r="L19" s="32">
@@ -2476,16 +2577,16 @@
     <row r="20" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45"/>
       <c r="B20" s="41">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="70" t="s">
         <v>68</v>
       </c>
       <c r="F20" s="47" t="s">
@@ -2494,7 +2595,7 @@
       <c r="G20" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="H20" s="30" t="s">
+      <c r="H20" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I20" s="47" t="s">
@@ -2503,7 +2604,7 @@
       <c r="J20" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="47">
         <v>1</v>
       </c>
       <c r="L20" s="47">
@@ -2518,16 +2619,16 @@
     <row r="21" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45"/>
       <c r="B21" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
       <c r="C21" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="32" t="s">
         <v>69</v>
       </c>
       <c r="F21" s="32" t="s">
@@ -2545,7 +2646,7 @@
       <c r="J21" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="80">
         <v>8</v>
       </c>
       <c r="L21" s="32">
@@ -2566,10 +2667,10 @@
       <c r="C22" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="70" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="47" t="s">
@@ -2578,7 +2679,7 @@
       <c r="G22" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I22" s="47" t="s">
@@ -2587,7 +2688,7 @@
       <c r="J22" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="47">
         <v>8</v>
       </c>
       <c r="L22" s="47">
@@ -2608,10 +2709,10 @@
       <c r="C23" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="32" t="s">
         <v>71</v>
       </c>
       <c r="F23" s="32" t="s">
@@ -2629,7 +2730,7 @@
       <c r="J23" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="80">
         <v>8</v>
       </c>
       <c r="L23" s="32">
@@ -2650,10 +2751,10 @@
       <c r="C24" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="70" t="s">
         <v>72</v>
       </c>
       <c r="F24" s="47" t="s">
@@ -2662,7 +2763,7 @@
       <c r="G24" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="H24" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I24" s="47" t="s">
@@ -2671,7 +2772,7 @@
       <c r="J24" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="47">
         <v>4</v>
       </c>
       <c r="L24" s="47">
@@ -2692,10 +2793,10 @@
       <c r="C25" s="58" t="s">
         <v>236</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="32" t="s">
         <v>73</v>
       </c>
       <c r="F25" s="32" t="s">
@@ -2713,7 +2814,7 @@
       <c r="J25" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="80">
         <v>1</v>
       </c>
       <c r="L25" s="32">
@@ -2734,10 +2835,10 @@
       <c r="C26" s="57" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="70" t="s">
         <v>74</v>
       </c>
       <c r="F26" s="47" t="s">
@@ -2746,7 +2847,7 @@
       <c r="G26" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="H26" s="30" t="s">
+      <c r="H26" s="47" t="s">
         <v>167</v>
       </c>
       <c r="I26" s="47" t="s">
@@ -2755,7 +2856,7 @@
       <c r="J26" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="47">
         <v>1</v>
       </c>
       <c r="L26" s="47">
@@ -2776,17 +2877,17 @@
       <c r="C27" s="58" t="s">
         <v>237</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="33" t="s">
+      <c r="E27" s="32" t="s">
         <v>75</v>
       </c>
       <c r="F27" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G27" s="71" t="s">
-        <v>147</v>
+      <c r="G27" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>168</v>
@@ -2797,7 +2898,7 @@
       <c r="J27" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="80">
         <v>1</v>
       </c>
       <c r="L27" s="32">
@@ -2818,10 +2919,10 @@
       <c r="C28" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="70" t="s">
         <v>76</v>
       </c>
       <c r="F28" s="47" t="s">
@@ -2830,7 +2931,7 @@
       <c r="G28" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="H28" s="47" t="s">
         <v>169</v>
       </c>
       <c r="I28" s="47" t="s">
@@ -2839,7 +2940,7 @@
       <c r="J28" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="47">
         <v>1</v>
       </c>
       <c r="L28" s="47">
@@ -2860,10 +2961,10 @@
       <c r="C29" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="32" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="32" t="s">
@@ -2881,7 +2982,7 @@
       <c r="J29" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="80">
         <v>8</v>
       </c>
       <c r="L29" s="32">
@@ -2902,10 +3003,10 @@
       <c r="C30" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="70" t="s">
         <v>78</v>
       </c>
       <c r="F30" s="47" t="s">
@@ -2914,14 +3015,16 @@
       <c r="G30" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="H30" s="30" t="s">
+      <c r="H30" s="47" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="47"/>
+      <c r="I30" s="47" t="s">
+        <v>200</v>
+      </c>
       <c r="J30" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="47">
         <v>4</v>
       </c>
       <c r="L30" s="47">
@@ -2940,17 +3043,17 @@
       <c r="C31" s="58" t="s">
         <v>237</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="32" t="s">
         <v>79</v>
       </c>
       <c r="F31" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="71">
-        <v>61300611121</v>
+      <c r="G31" s="32" t="s">
+        <v>221</v>
       </c>
       <c r="H31" s="32" t="s">
         <v>171</v>
@@ -2961,7 +3064,7 @@
       <c r="J31" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="80">
         <v>1</v>
       </c>
       <c r="L31" s="32">
@@ -3003,7 +3106,7 @@
       <c r="J32" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="K32" s="53">
+      <c r="K32" s="49">
         <v>5</v>
       </c>
       <c r="L32" s="49">
@@ -3015,28 +3118,28 @@
       </c>
       <c r="N32" s="49"/>
     </row>
-    <row r="33" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="45"/>
-      <c r="B33" s="41">
+      <c r="B33" s="78">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="59" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="48" t="s">
         <v>81</v>
       </c>
       <c r="F33" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="71" t="s">
-        <v>148</v>
-      </c>
-      <c r="H33" s="32" t="s">
+      <c r="G33" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="H33" s="48" t="s">
         <v>168</v>
       </c>
       <c r="I33" s="48" t="s">
@@ -3045,7 +3148,7 @@
       <c r="J33" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="81">
         <v>3</v>
       </c>
       <c r="L33" s="48">
@@ -3066,10 +3169,10 @@
       <c r="C34" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="E34" s="70" t="s">
         <v>82</v>
       </c>
       <c r="F34" s="47" t="s">
@@ -3078,7 +3181,7 @@
       <c r="G34" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="H34" s="30" t="s">
+      <c r="H34" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I34" s="47" t="s">
@@ -3087,7 +3190,7 @@
       <c r="J34" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="47">
         <v>8</v>
       </c>
       <c r="L34" s="47">
@@ -3108,10 +3211,10 @@
       <c r="C35" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="32" t="s">
+      <c r="D35" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="33" t="s">
+      <c r="E35" s="32" t="s">
         <v>83</v>
       </c>
       <c r="F35" s="32" t="s">
@@ -3129,7 +3232,7 @@
       <c r="J35" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="80">
         <v>3</v>
       </c>
       <c r="L35" s="32">
@@ -3150,10 +3253,10 @@
       <c r="C36" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="E36" s="31" t="s">
+      <c r="E36" s="70" t="s">
         <v>84</v>
       </c>
       <c r="F36" s="47" t="s">
@@ -3162,7 +3265,7 @@
       <c r="G36" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="H36" s="30" t="s">
+      <c r="H36" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I36" s="47" t="s">
@@ -3171,7 +3274,7 @@
       <c r="J36" s="50" t="s">
         <v>193</v>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="47">
         <v>10</v>
       </c>
       <c r="L36" s="47">
@@ -3192,10 +3295,10 @@
       <c r="C37" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="D37" s="32" t="s">
+      <c r="D37" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E37" s="32" t="s">
         <v>85</v>
       </c>
       <c r="F37" s="32" t="s">
@@ -3213,7 +3316,7 @@
       <c r="J37" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="K37" s="32">
+      <c r="K37" s="80">
         <v>2</v>
       </c>
       <c r="L37" s="32">
@@ -3234,10 +3337,10 @@
       <c r="C38" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="D38" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E38" s="31" t="s">
+      <c r="D38" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="E38" s="70" t="s">
         <v>86</v>
       </c>
       <c r="F38" s="47" t="s">
@@ -3246,7 +3349,7 @@
       <c r="G38" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="47" t="s">
         <v>161</v>
       </c>
       <c r="I38" s="47" t="s">
@@ -3255,7 +3358,7 @@
       <c r="J38" s="50" t="s">
         <v>195</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="47">
         <v>17</v>
       </c>
       <c r="L38" s="47">
@@ -3270,16 +3373,16 @@
     <row r="39" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="45"/>
       <c r="B39" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
       <c r="C39" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="32" t="s">
         <v>87</v>
       </c>
       <c r="F39" s="32" t="s">
@@ -3297,7 +3400,7 @@
       <c r="J39" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="80">
         <v>4</v>
       </c>
       <c r="L39" s="32">
@@ -3312,7 +3415,7 @@
     <row r="40" spans="1:14" s="46" customFormat="1" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="45"/>
       <c r="B40" s="41">
-        <f>ROW(B40) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="57" t="s">
@@ -3330,14 +3433,16 @@
       <c r="G40" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="H40" s="49"/>
+      <c r="H40" s="49" t="s">
+        <v>200</v>
+      </c>
       <c r="I40" s="49" t="s">
         <v>200</v>
       </c>
       <c r="J40" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="K40" s="53">
+      <c r="K40" s="49">
         <v>106</v>
       </c>
       <c r="L40" s="53">
@@ -3352,16 +3457,16 @@
     <row r="41" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="45"/>
       <c r="B41" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="58" t="s">
         <v>241</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="32" t="s">
         <v>89</v>
       </c>
       <c r="F41" s="32" t="s">
@@ -3374,12 +3479,12 @@
         <v>169</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="J41" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="80">
         <v>1</v>
       </c>
       <c r="L41" s="32">
@@ -3394,16 +3499,16 @@
     <row r="42" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="45"/>
       <c r="B42" s="41">
-        <f>ROW(B42) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="70" t="s">
         <v>90</v>
       </c>
       <c r="F42" s="47" t="s">
@@ -3412,7 +3517,7 @@
       <c r="G42" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="H42" s="30" t="s">
+      <c r="H42" s="47" t="s">
         <v>172</v>
       </c>
       <c r="I42" s="47" t="s">
@@ -3421,7 +3526,7 @@
       <c r="J42" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K42" s="30">
+      <c r="K42" s="47">
         <v>1</v>
       </c>
       <c r="L42" s="47">
@@ -3436,16 +3541,16 @@
     <row r="43" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="45"/>
       <c r="B43" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
       <c r="C43" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="33" t="s">
+      <c r="E43" s="32" t="s">
         <v>91</v>
       </c>
       <c r="F43" s="32" t="s">
@@ -3463,7 +3568,7 @@
       <c r="J43" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K43" s="32">
+      <c r="K43" s="80">
         <v>8</v>
       </c>
       <c r="L43" s="32">
@@ -3478,16 +3583,16 @@
     <row r="44" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="45"/>
       <c r="B44" s="41">
-        <f>ROW(B44) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C44" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="31" t="s">
+      <c r="E44" s="70" t="s">
         <v>92</v>
       </c>
       <c r="F44" s="47" t="s">
@@ -3496,7 +3601,7 @@
       <c r="G44" s="70" t="s">
         <v>156</v>
       </c>
-      <c r="H44" s="30" t="s">
+      <c r="H44" s="47" t="s">
         <v>173</v>
       </c>
       <c r="I44" s="47" t="s">
@@ -3505,7 +3610,7 @@
       <c r="J44" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K44" s="30">
+      <c r="K44" s="47">
         <v>1</v>
       </c>
       <c r="L44" s="47">
@@ -3520,16 +3625,16 @@
     <row r="45" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="45"/>
       <c r="B45" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
       <c r="C45" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="33" t="s">
+      <c r="E45" s="32" t="s">
         <v>93</v>
       </c>
       <c r="F45" s="32" t="s">
@@ -3541,11 +3646,13 @@
       <c r="H45" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="I45" s="32"/>
+      <c r="I45" s="32" t="s">
+        <v>200</v>
+      </c>
       <c r="J45" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="80">
         <v>1</v>
       </c>
       <c r="L45" s="32">
@@ -3560,16 +3667,16 @@
     <row r="46" spans="1:14" s="46" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="45"/>
       <c r="B46" s="41">
-        <f>ROW(B46) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C46" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" s="70" t="s">
         <v>94</v>
       </c>
       <c r="F46" s="47" t="s">
@@ -3578,7 +3685,7 @@
       <c r="G46" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="H46" s="30" t="s">
+      <c r="H46" s="47" t="s">
         <v>167</v>
       </c>
       <c r="I46" s="47" t="s">
@@ -3587,7 +3694,7 @@
       <c r="J46" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K46" s="30">
+      <c r="K46" s="47">
         <v>2</v>
       </c>
       <c r="L46" s="47">
@@ -3602,34 +3709,34 @@
     <row r="47" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="45"/>
       <c r="B47" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
       <c r="C47" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="E47" s="33" t="s">
+      <c r="E47" s="32" t="s">
         <v>95</v>
       </c>
       <c r="F47" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="G47" s="33" t="s">
-        <v>125</v>
+      <c r="G47" s="32" t="s">
+        <v>263</v>
       </c>
       <c r="H47" s="32" t="s">
         <v>174</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="J47" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="80">
         <v>1</v>
       </c>
       <c r="L47" s="32">
@@ -3644,16 +3751,16 @@
     <row r="48" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="45"/>
       <c r="B48" s="41">
-        <f>ROW(B48) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="E48" s="31" t="s">
+      <c r="E48" s="70" t="s">
         <v>96</v>
       </c>
       <c r="F48" s="47" t="s">
@@ -3662,14 +3769,16 @@
       <c r="G48" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="H48" s="30" t="s">
+      <c r="H48" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="I48" s="47"/>
+      <c r="I48" s="47" t="s">
+        <v>200</v>
+      </c>
       <c r="J48" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="K48" s="30">
+      <c r="K48" s="47">
         <v>1</v>
       </c>
       <c r="L48" s="47">
@@ -3684,16 +3793,16 @@
     <row r="49" spans="1:14" s="46" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="45"/>
       <c r="B49" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
       <c r="C49" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="E49" s="33" t="s">
+      <c r="E49" s="32" t="s">
         <v>97</v>
       </c>
       <c r="F49" s="32" t="s">
@@ -3705,11 +3814,13 @@
       <c r="H49" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="I49" s="32"/>
+      <c r="I49" s="32" t="s">
+        <v>200</v>
+      </c>
       <c r="J49" s="51" t="s">
         <v>200</v>
       </c>
-      <c r="K49" s="32">
+      <c r="K49" s="80">
         <v>4</v>
       </c>
       <c r="L49" s="32">
@@ -3724,16 +3835,16 @@
     <row r="50" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="45"/>
       <c r="B50" s="41">
-        <f>ROW(B50) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C50" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="D50" s="30" t="s">
+      <c r="D50" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="E50" s="31" t="s">
+      <c r="E50" s="70" t="s">
         <v>98</v>
       </c>
       <c r="F50" s="47" t="s">
@@ -3742,7 +3853,7 @@
       <c r="G50" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="H50" s="30" t="s">
+      <c r="H50" s="47" t="s">
         <v>176</v>
       </c>
       <c r="I50" s="47" t="s">
@@ -3751,7 +3862,7 @@
       <c r="J50" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="K50" s="30">
+      <c r="K50" s="47">
         <v>1</v>
       </c>
       <c r="L50" s="47">
@@ -3766,19 +3877,19 @@
     <row r="51" spans="1:14" s="46" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="45"/>
       <c r="B51" s="41">
-        <f t="shared" si="0"/>
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
       <c r="C51" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="E51" s="33" t="s">
+      <c r="E51" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="F51" s="54" t="s">
+      <c r="F51" s="32" t="s">
         <v>244</v>
       </c>
       <c r="G51" s="33" t="s">
@@ -3793,7 +3904,7 @@
       <c r="J51" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="54">
         <v>2</v>
       </c>
       <c r="L51" s="32">
@@ -4791,7 +4902,7 @@
       </c>
       <c r="N27" s="32"/>
     </row>
-    <row r="28" spans="1:14" s="46" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45"/>
       <c r="B28" s="41">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -6743,7 +6854,7 @@
       </c>
       <c r="N27" s="32"/>
     </row>
-    <row r="28" spans="1:14" s="46" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" s="46" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45"/>
       <c r="B28" s="41">
         <f>ROW(B28) - ROW($B$9)</f>
